--- a/data/dashboard.xlsx
+++ b/data/dashboard.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +42,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -74,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -82,6 +85,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -205,12 +209,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$B$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -239,12 +243,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$C$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -273,12 +277,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$D$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$3</f>
             </numRef>
           </val>
         </ser>
@@ -307,12 +311,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$E$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$3</f>
             </numRef>
           </val>
         </ser>
@@ -341,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$F$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$3</f>
             </numRef>
           </val>
         </ser>
@@ -375,12 +379,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$G$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$3</f>
             </numRef>
           </val>
         </ser>
@@ -409,12 +413,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$H$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$3</f>
             </numRef>
           </val>
         </ser>
@@ -443,12 +447,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$I$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$3</f>
             </numRef>
           </val>
         </ser>
@@ -477,12 +481,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$J$2</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$3</f>
             </numRef>
           </val>
         </ser>
@@ -598,12 +602,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2</f>
+              <f>'Verloop GC-punten'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$B$2</f>
+              <f>'Verloop GC-punten'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -632,12 +636,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2</f>
+              <f>'Verloop GC-punten'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$C$2</f>
+              <f>'Verloop GC-punten'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -666,12 +670,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2</f>
+              <f>'Verloop GC-punten'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$D$2</f>
+              <f>'Verloop GC-punten'!$D$2:$D$3</f>
             </numRef>
           </val>
         </ser>
@@ -700,12 +704,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2</f>
+              <f>'Verloop GC-punten'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$E$2</f>
+              <f>'Verloop GC-punten'!$E$2:$E$3</f>
             </numRef>
           </val>
         </ser>
@@ -734,12 +738,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2</f>
+              <f>'Verloop GC-punten'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$F$2</f>
+              <f>'Verloop GC-punten'!$F$2:$F$3</f>
             </numRef>
           </val>
         </ser>
@@ -768,12 +772,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2</f>
+              <f>'Verloop GC-punten'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$G$2</f>
+              <f>'Verloop GC-punten'!$G$2:$G$3</f>
             </numRef>
           </val>
         </ser>
@@ -802,12 +806,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2</f>
+              <f>'Verloop GC-punten'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$H$2</f>
+              <f>'Verloop GC-punten'!$H$2:$H$3</f>
             </numRef>
           </val>
         </ser>
@@ -836,12 +840,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2</f>
+              <f>'Verloop GC-punten'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$I$2</f>
+              <f>'Verloop GC-punten'!$I$2:$I$3</f>
             </numRef>
           </val>
         </ser>
@@ -870,12 +874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2</f>
+              <f>'Verloop GC-punten'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$J$2</f>
+              <f>'Verloop GC-punten'!$J$2:$J$3</f>
             </numRef>
           </val>
         </ser>
@@ -991,12 +995,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$B$2</f>
+              <f>'Verloop Puntenklassement'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -1025,12 +1029,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$C$2</f>
+              <f>'Verloop Puntenklassement'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -1059,12 +1063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$D$2</f>
+              <f>'Verloop Puntenklassement'!$D$2:$D$3</f>
             </numRef>
           </val>
         </ser>
@@ -1093,12 +1097,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$E$2</f>
+              <f>'Verloop Puntenklassement'!$E$2:$E$3</f>
             </numRef>
           </val>
         </ser>
@@ -1127,12 +1131,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$F$2</f>
+              <f>'Verloop Puntenklassement'!$F$2:$F$3</f>
             </numRef>
           </val>
         </ser>
@@ -1161,12 +1165,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$G$2</f>
+              <f>'Verloop Puntenklassement'!$G$2:$G$3</f>
             </numRef>
           </val>
         </ser>
@@ -1195,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$H$2</f>
+              <f>'Verloop Puntenklassement'!$H$2:$H$3</f>
             </numRef>
           </val>
         </ser>
@@ -1229,12 +1233,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$I$2</f>
+              <f>'Verloop Puntenklassement'!$I$2:$I$3</f>
             </numRef>
           </val>
         </ser>
@@ -1263,12 +1267,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$J$2</f>
+              <f>'Verloop Puntenklassement'!$J$2:$J$3</f>
             </numRef>
           </val>
         </ser>
@@ -1384,12 +1388,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$B$2</f>
+              <f>'Verloop Bergklassement'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -1418,12 +1422,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$C$2</f>
+              <f>'Verloop Bergklassement'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -1452,12 +1456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$D$2</f>
+              <f>'Verloop Bergklassement'!$D$2:$D$3</f>
             </numRef>
           </val>
         </ser>
@@ -1486,12 +1490,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$E$2</f>
+              <f>'Verloop Bergklassement'!$E$2:$E$3</f>
             </numRef>
           </val>
         </ser>
@@ -1520,12 +1524,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$F$2</f>
+              <f>'Verloop Bergklassement'!$F$2:$F$3</f>
             </numRef>
           </val>
         </ser>
@@ -1554,12 +1558,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$G$2</f>
+              <f>'Verloop Bergklassement'!$G$2:$G$3</f>
             </numRef>
           </val>
         </ser>
@@ -1588,12 +1592,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$H$2</f>
+              <f>'Verloop Bergklassement'!$H$2:$H$3</f>
             </numRef>
           </val>
         </ser>
@@ -1622,12 +1626,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$I$2</f>
+              <f>'Verloop Bergklassement'!$I$2:$I$3</f>
             </numRef>
           </val>
         </ser>
@@ -1656,12 +1660,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$J$2</f>
+              <f>'Verloop Bergklassement'!$J$2:$J$3</f>
             </numRef>
           </val>
         </ser>
@@ -2127,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2208,27 +2212,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2243,7 +2247,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>272</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -2251,27 +2255,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2286,7 +2290,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>251</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2294,27 +2298,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2329,7 +2333,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>245</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2337,27 +2341,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2372,7 +2376,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>229</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2380,27 +2384,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2415,7 +2419,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>219</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -2423,27 +2427,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2458,7 +2462,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>193</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -2466,27 +2470,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2501,7 +2505,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>191</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2509,27 +2513,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2544,7 +2548,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>189</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2552,27 +2556,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>59</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2587,7 +2591,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -3090,7 +3094,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3110,7 +3114,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3125,7 +3129,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3133,7 +3137,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3153,7 +3157,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3168,7 +3172,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3176,7 +3180,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3196,7 +3200,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3211,187 +3215,54 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Immer geradeaus</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-    </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Pan y aqua</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Jongerenklassement</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Belahu</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>IY</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>H2H</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3401,7 +3272,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3411,25 +3282,10 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3444,7 +3300,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3454,69 +3310,127 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Tour MondAIl</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Alegría</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Jongerenklassement</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Participant</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>IY</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Pts</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>H2H</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3526,7 +3440,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3536,7 +3450,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -3544,7 +3458,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3554,7 +3468,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3564,7 +3478,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3572,7 +3486,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3582,7 +3496,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3592,178 +3506,10 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Alegría</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Belahu</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Immer geradeaus</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Pan y aqua</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Not_Kermit</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3776,7 +3522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3877,6 +3623,40 @@
         <v>61</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>146</v>
+      </c>
+      <c r="C3" t="n">
+        <v>180</v>
+      </c>
+      <c r="D3" t="n">
+        <v>126</v>
+      </c>
+      <c r="E3" t="n">
+        <v>168</v>
+      </c>
+      <c r="F3" t="n">
+        <v>135</v>
+      </c>
+      <c r="G3" t="n">
+        <v>137</v>
+      </c>
+      <c r="H3" t="n">
+        <v>212</v>
+      </c>
+      <c r="I3" t="n">
+        <v>198</v>
+      </c>
+      <c r="J3" t="n">
+        <v>184</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3889,7 +3669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3990,6 +3770,40 @@
         <v>40</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" t="n">
+        <v>29</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>46</v>
+      </c>
+      <c r="I3" t="n">
+        <v>42</v>
+      </c>
+      <c r="J3" t="n">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4002,7 +3816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4076,6 +3890,40 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>127</v>
+      </c>
+      <c r="D3" t="n">
+        <v>89</v>
+      </c>
+      <c r="E3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F3" t="n">
+        <v>87</v>
+      </c>
+      <c r="G3" t="n">
+        <v>92</v>
+      </c>
+      <c r="H3" t="n">
+        <v>143</v>
+      </c>
+      <c r="I3" t="n">
+        <v>137</v>
+      </c>
+      <c r="J3" t="n">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4088,7 +3936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4162,6 +4010,40 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4174,8 +4056,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -4185,10 +4073,349 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Nog niet genoeg etappes met data (minimaal 2 nodig).</t>
-        </is>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Laatste etappe</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Deelnemer</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Punten toen</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Punten nu</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Verschil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SexySeixas</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C5" t="n">
+        <v>212</v>
+      </c>
+      <c r="D5" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tour MondAIl</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>53</v>
+      </c>
+      <c r="C6" t="n">
+        <v>198</v>
+      </c>
+      <c r="D6" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>49</v>
+      </c>
+      <c r="C7" t="n">
+        <v>180</v>
+      </c>
+      <c r="D7" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Yellow bitch</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>61</v>
+      </c>
+      <c r="C8" t="n">
+        <v>184</v>
+      </c>
+      <c r="D8" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>51</v>
+      </c>
+      <c r="C9" t="n">
+        <v>168</v>
+      </c>
+      <c r="D9" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Alegría</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>45</v>
+      </c>
+      <c r="C10" t="n">
+        <v>146</v>
+      </c>
+      <c r="D10" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Not_Kermit</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>51</v>
+      </c>
+      <c r="C11" t="n">
+        <v>135</v>
+      </c>
+      <c r="D11" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>56</v>
+      </c>
+      <c r="C12" t="n">
+        <v>137</v>
+      </c>
+      <c r="D12" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Immer geradeaus</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>63</v>
+      </c>
+      <c r="C13" t="n">
+        <v>126</v>
+      </c>
+      <c r="D13" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Laatste 7 etappes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Deelnemer</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Punten toen</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Punten nu</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Verschil</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SexySeixas</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>60</v>
+      </c>
+      <c r="C18" t="n">
+        <v>212</v>
+      </c>
+      <c r="D18" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Tour MondAIl</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>53</v>
+      </c>
+      <c r="C19" t="n">
+        <v>198</v>
+      </c>
+      <c r="D19" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>49</v>
+      </c>
+      <c r="C20" t="n">
+        <v>180</v>
+      </c>
+      <c r="D20" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Yellow bitch</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>61</v>
+      </c>
+      <c r="C21" t="n">
+        <v>184</v>
+      </c>
+      <c r="D21" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>51</v>
+      </c>
+      <c r="C22" t="n">
+        <v>168</v>
+      </c>
+      <c r="D22" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Alegría</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>45</v>
+      </c>
+      <c r="C23" t="n">
+        <v>146</v>
+      </c>
+      <c r="D23" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Not_Kermit</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>51</v>
+      </c>
+      <c r="C24" t="n">
+        <v>135</v>
+      </c>
+      <c r="D24" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>56</v>
+      </c>
+      <c r="C25" t="n">
+        <v>137</v>
+      </c>
+      <c r="D25" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Immer geradeaus</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>63</v>
+      </c>
+      <c r="C26" t="n">
+        <v>126</v>
+      </c>
+      <c r="D26" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4202,7 +4429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4217,7 +4444,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Most picked (renners)</t>
         </is>
@@ -4295,7 +4522,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4556,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4590,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4624,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4658,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4692,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4726,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4760,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -4567,7 +4794,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4998,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4805,7 +5032,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -4839,7 +5066,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -4907,7 +5134,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5372,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5508,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5814,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5882,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -5995,7 +6222,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6290,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6397,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Most points (renners)</t>
         </is>
@@ -6221,46 +6448,46 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Vingegaard, Jonas</t>
+          <t>Pogačar, Tadej</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/jonas-vingegaard-rasmussen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tadej-pogacar/2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TVL</t>
+          <t>UAD</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>100.0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pogačar, Tadej</t>
+          <t>Del Toro, Isaac</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tadej-pogacar/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/isaac-del-toro/2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6271,605 +6498,1081 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ganna, Filippo</t>
+          <t>Vingegaard, Jonas</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jonas-vingegaard-rasmussen/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>TVL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>88.9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ayuso, Juan</t>
+          <t>Evenepoel, Remco</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/remco-evenepoel/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Evenepoel, Remco</t>
+          <t>Ayuso, Juan</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/remco-evenepoel/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Vauquelin, Kévin</t>
+          <t>Seixas, Paul</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/paul-seixas/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Del Toro, Isaac</t>
+          <t>Girmay, Biniam</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/isaac-del-toro/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/biniam-girmay/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UAD</t>
+          <t>NSN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Arensman, Thymen</t>
+          <t>Carapaz, Richard</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>EFE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>55.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Pedersen, Mads</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/mads-pedersen/2026</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>LTK</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>33.3</t>
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Pidcock, Tom</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PQT</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+    </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>History (eerdere jaren)</t>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Van Eetvelt, Lennert</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/lennert-van-eetvelt/2026</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>LOI</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>general_winner</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>points_winner</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>mountain_winner</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>youth_winner</t>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Ganna, Filippo</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Philipsen, Jasper</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Tour MondAIl</t>
-        </is>
-      </c>
+          <t>APT</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Merlier, Tim</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tim-merlier/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
-        </is>
-      </c>
+          <t>SOQ</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Van Wilder, Ilan</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Yellow bitch</t>
-        </is>
-      </c>
+          <t>SOQ</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>Kanter, Max</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>https://www.worldcyclingstats.com/en/rider/max-kanter/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Pan y aqua</t>
-        </is>
-      </c>
+          <t>XAT</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>Lipowitz, Florian</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>https://www.worldcyclingstats.com/en/rider/florian-lipowitz/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Plak-bidon</t>
-        </is>
-      </c>
+          <t>RBH</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Uijtdebroeks, Cian</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Tour d'Hans</t>
-        </is>
-      </c>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>vlammie</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>Vauquelin, Kévin</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Tour d'Hans</t>
-        </is>
-      </c>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>Arensman, Thymen</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Belahu</t>
-        </is>
-      </c>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>Foss, Tobias</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tobias-foss/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belahu</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Chi’s cycling</t>
-        </is>
-      </c>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>Wellens, Tim</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/tim-wellens/2026</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>UAD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>55.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>History (eerdere jaren)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>general_winner</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>points_winner</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>mountain_winner</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>youth_winner</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SexySeixas</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SexySeixas</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>SexySeixas</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Not Kermit</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Not Kermit</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SexySeixas</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SexySeixas</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Yellow bitch</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Not Kermit</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Plak-bidon</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Not Kermit</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tour MondAIl</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Tour d'Hans</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>vlammie</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Tour d'Hans</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Tour MondAIl</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Chi’s cycling</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>Bismarck</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Not Kermit</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>Bismarck</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>Belahu</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>Ga-toch-fietsuh</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Pan y aqua</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>Ga-toch-fietsuh</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>Ko-fidis</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>Ko-fidis</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Ko-fidis</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>Belahu</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>Bismarck</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>The O Team</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Pan y aqua</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>The O Team</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>Ko-fidis</t>
         </is>

--- a/data/dashboard.xlsx
+++ b/data/dashboard.xlsx
@@ -2131,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2653,7 +2653,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2673,12 +2673,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2696,7 +2696,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,7 +2739,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,7 +2782,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,7 +2825,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,7 +2868,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2911,7 +2911,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,7 +2954,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,7 +2997,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3220,49 +3220,182 @@
       </c>
       <c r="I33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SexySeixas</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+    </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Jongerenklassement</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Tour MondAIl</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Participant</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>IY</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Pts</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>H2H</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3272,7 +3405,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3282,10 +3415,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3300,7 +3448,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3310,137 +3458,79 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Tour MondAIl</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Alegría</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Belahu</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Jongerenklassement</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>IY</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>H2H</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3450,7 +3540,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -3458,17 +3548,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3478,7 +3568,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3486,30 +3576,198 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Tour MondAIl</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Alegría</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Immer geradeaus</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Not_Kermit</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/dashboard.xlsx
+++ b/data/dashboard.xlsx
@@ -209,12 +209,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -277,12 +277,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -311,12 +311,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$4</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -379,12 +379,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$4</f>
             </numRef>
           </val>
         </ser>
@@ -413,12 +413,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$4</f>
             </numRef>
           </val>
         </ser>
@@ -447,12 +447,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$4</f>
             </numRef>
           </val>
         </ser>
@@ -481,12 +481,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$3</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$4</f>
             </numRef>
           </val>
         </ser>
@@ -602,12 +602,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$3</f>
+              <f>'Verloop GC-punten'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$B$2:$B$3</f>
+              <f>'Verloop GC-punten'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -636,12 +636,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$3</f>
+              <f>'Verloop GC-punten'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$C$2:$C$3</f>
+              <f>'Verloop GC-punten'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -670,12 +670,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$3</f>
+              <f>'Verloop GC-punten'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$D$2:$D$3</f>
+              <f>'Verloop GC-punten'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -704,12 +704,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$3</f>
+              <f>'Verloop GC-punten'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$E$2:$E$3</f>
+              <f>'Verloop GC-punten'!$E$2:$E$4</f>
             </numRef>
           </val>
         </ser>
@@ -738,12 +738,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$3</f>
+              <f>'Verloop GC-punten'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$F$2:$F$3</f>
+              <f>'Verloop GC-punten'!$F$2:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$3</f>
+              <f>'Verloop GC-punten'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$G$2:$G$3</f>
+              <f>'Verloop GC-punten'!$G$2:$G$4</f>
             </numRef>
           </val>
         </ser>
@@ -806,12 +806,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$3</f>
+              <f>'Verloop GC-punten'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$H$2:$H$3</f>
+              <f>'Verloop GC-punten'!$H$2:$H$4</f>
             </numRef>
           </val>
         </ser>
@@ -840,12 +840,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$3</f>
+              <f>'Verloop GC-punten'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$I$2:$I$3</f>
+              <f>'Verloop GC-punten'!$I$2:$I$4</f>
             </numRef>
           </val>
         </ser>
@@ -874,12 +874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$3</f>
+              <f>'Verloop GC-punten'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$J$2:$J$3</f>
+              <f>'Verloop GC-punten'!$J$2:$J$4</f>
             </numRef>
           </val>
         </ser>
@@ -995,12 +995,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$B$2:$B$3</f>
+              <f>'Verloop Puntenklassement'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -1029,12 +1029,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$C$2:$C$3</f>
+              <f>'Verloop Puntenklassement'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -1063,12 +1063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$D$2:$D$3</f>
+              <f>'Verloop Puntenklassement'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -1097,12 +1097,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$E$2:$E$3</f>
+              <f>'Verloop Puntenklassement'!$E$2:$E$4</f>
             </numRef>
           </val>
         </ser>
@@ -1131,12 +1131,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$F$2:$F$3</f>
+              <f>'Verloop Puntenklassement'!$F$2:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -1165,12 +1165,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$G$2:$G$3</f>
+              <f>'Verloop Puntenklassement'!$G$2:$G$4</f>
             </numRef>
           </val>
         </ser>
@@ -1199,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$H$2:$H$3</f>
+              <f>'Verloop Puntenklassement'!$H$2:$H$4</f>
             </numRef>
           </val>
         </ser>
@@ -1233,12 +1233,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$I$2:$I$3</f>
+              <f>'Verloop Puntenklassement'!$I$2:$I$4</f>
             </numRef>
           </val>
         </ser>
@@ -1267,12 +1267,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$3</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$J$2:$J$3</f>
+              <f>'Verloop Puntenklassement'!$J$2:$J$4</f>
             </numRef>
           </val>
         </ser>
@@ -1388,12 +1388,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$B$2:$B$3</f>
+              <f>'Verloop Bergklassement'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -1422,12 +1422,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$C$2:$C$3</f>
+              <f>'Verloop Bergklassement'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -1456,12 +1456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$D$2:$D$3</f>
+              <f>'Verloop Bergklassement'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -1490,12 +1490,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$E$2:$E$3</f>
+              <f>'Verloop Bergklassement'!$E$2:$E$4</f>
             </numRef>
           </val>
         </ser>
@@ -1524,12 +1524,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$F$2:$F$3</f>
+              <f>'Verloop Bergklassement'!$F$2:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -1558,12 +1558,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$G$2:$G$3</f>
+              <f>'Verloop Bergklassement'!$G$2:$G$4</f>
             </numRef>
           </val>
         </ser>
@@ -1592,12 +1592,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$H$2:$H$3</f>
+              <f>'Verloop Bergklassement'!$H$2:$H$4</f>
             </numRef>
           </val>
         </ser>
@@ -1626,12 +1626,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$I$2:$I$3</f>
+              <f>'Verloop Bergklassement'!$I$2:$I$4</f>
             </numRef>
           </val>
         </ser>
@@ -1660,12 +1660,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$3</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$J$2:$J$3</f>
+              <f>'Verloop Bergklassement'!$J$2:$J$4</f>
             </numRef>
           </val>
         </ser>
@@ -2217,22 +2217,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>256</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>134</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>461</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -2260,27 +2260,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>239</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>121</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>426</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2303,22 +2303,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>418</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2346,22 +2346,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>221</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>102</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>390</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2389,22 +2389,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>197</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>363</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>162</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>318</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -2470,27 +2470,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>309</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2518,27 +2518,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>149</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>97</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>304</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2556,27 +2556,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>160</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>301</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2668,17 +2668,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>256</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2711,17 +2711,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>239</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2754,17 +2754,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>221</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2797,17 +2797,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>216</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>197</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,7 +2868,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2878,22 +2878,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>162</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2911,7 +2911,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,7 +3094,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3137,7 +3137,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -3352,7 +3352,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -3525,12 +3525,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -3553,12 +3553,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -3665,14 +3665,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>-</t>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -3693,14 +3693,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>-</t>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3915,6 +3915,40 @@
         <v>184</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>110</v>
+      </c>
+      <c r="C4" t="n">
+        <v>161</v>
+      </c>
+      <c r="D4" t="n">
+        <v>116</v>
+      </c>
+      <c r="E4" t="n">
+        <v>144</v>
+      </c>
+      <c r="F4" t="n">
+        <v>123</v>
+      </c>
+      <c r="G4" t="n">
+        <v>125</v>
+      </c>
+      <c r="H4" t="n">
+        <v>189</v>
+      </c>
+      <c r="I4" t="n">
+        <v>176</v>
+      </c>
+      <c r="J4" t="n">
+        <v>173</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3927,7 +3961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4062,6 +4096,40 @@
         <v>46</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D4" t="n">
+        <v>34</v>
+      </c>
+      <c r="E4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F4" t="n">
+        <v>34</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" t="n">
+        <v>49</v>
+      </c>
+      <c r="I4" t="n">
+        <v>47</v>
+      </c>
+      <c r="J4" t="n">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4074,7 +4142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4182,6 +4250,40 @@
         <v>119</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>60</v>
+      </c>
+      <c r="C4" t="n">
+        <v>94</v>
+      </c>
+      <c r="D4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E4" t="n">
+        <v>82</v>
+      </c>
+      <c r="F4" t="n">
+        <v>54</v>
+      </c>
+      <c r="G4" t="n">
+        <v>70</v>
+      </c>
+      <c r="H4" t="n">
+        <v>113</v>
+      </c>
+      <c r="I4" t="n">
+        <v>102</v>
+      </c>
+      <c r="J4" t="n">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4194,7 +4296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4300,6 +4402,40 @@
       </c>
       <c r="J3" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4362,145 +4498,145 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="C5" t="n">
-        <v>212</v>
+        <v>116</v>
       </c>
       <c r="D5" t="n">
-        <v>152</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>184</v>
       </c>
       <c r="C6" t="n">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="D6" t="n">
-        <v>145</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>180</v>
+        <v>123</v>
       </c>
       <c r="D7" t="n">
-        <v>131</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="C8" t="n">
-        <v>184</v>
+        <v>125</v>
       </c>
       <c r="D8" t="n">
-        <v>123</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>180</v>
       </c>
       <c r="C9" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D9" t="n">
-        <v>117</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>198</v>
       </c>
       <c r="C10" t="n">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>101</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>212</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>84</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>168</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>81</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="16">
@@ -4542,10 +4678,10 @@
         <v>60</v>
       </c>
       <c r="C18" t="n">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="D18" t="n">
-        <v>152</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
@@ -4558,10 +4694,10 @@
         <v>53</v>
       </c>
       <c r="C19" t="n">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="D19" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20">
@@ -4574,10 +4710,10 @@
         <v>49</v>
       </c>
       <c r="C20" t="n">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="D20" t="n">
-        <v>131</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21">
@@ -4590,10 +4726,10 @@
         <v>61</v>
       </c>
       <c r="C21" t="n">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D21" t="n">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22">
@@ -4606,58 +4742,58 @@
         <v>51</v>
       </c>
       <c r="C22" t="n">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C23" t="n">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="D23" t="n">
-        <v>101</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C24" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D24" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C25" t="n">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="D25" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26">
@@ -4670,10 +4806,10 @@
         <v>63</v>
       </c>
       <c r="C26" t="n">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4687,7 +4823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4780,7 +4916,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>91</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4950,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4984,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -4950,7 +5086,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -4984,7 +5120,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5154,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>64</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5392,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5426,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5528,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5902,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6140,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6378,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6412,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6684,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6858,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>91</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -6740,68 +6876,68 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Del Toro, Isaac</t>
+          <t>Vingegaard, Jonas</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/isaac-del-toro/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jonas-vingegaard-rasmussen/2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UAD</t>
+          <t>TVL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>88.9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Vingegaard, Jonas</t>
+          <t>Del Toro, Isaac</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/jonas-vingegaard-rasmussen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/isaac-del-toro/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TVL</t>
+          <t>UAD</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6960,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -6842,102 +6978,102 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ayuso, Juan</t>
+          <t>Seixas, Paul</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/paul-seixas/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Seixas, Paul</t>
+          <t>Ayuso, Juan</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/paul-seixas/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DCT</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Girmay, Biniam</t>
+          <t>Pedersen, Mads</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/biniam-girmay/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mads-pedersen/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NSN</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
@@ -6960,7 +7096,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -6978,57 +7114,57 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Pedersen, Mads</t>
+          <t>Van Eetvelt, Lennert</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mads-pedersen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/lennert-van-eetvelt/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Pidcock, Tom</t>
+          <t>Lipowitz, Florian</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/florian-lipowitz/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PQT</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -7046,23 +7182,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Van Eetvelt, Lennert</t>
+          <t>Girmay, Biniam</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/lennert-van-eetvelt/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/biniam-girmay/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>NSN</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -7080,159 +7216,159 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ganna, Filippo</t>
+          <t>Van Wilder, Ilan</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Philipsen, Jasper</t>
+          <t>Pidcock, Tom</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>PQT</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Merlier, Tim</t>
+          <t>Ganna, Filippo</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tim-merlier/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Van Wilder, Ilan</t>
+          <t>Philipsen, Jasper</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kanter, Max</t>
+          <t>Cort, Magnus</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/max-kanter/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/magnus-cort-nielsen/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>XAT</t>
+          <t>UXM</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -7250,57 +7386,57 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Lipowitz, Florian</t>
+          <t>Merlier, Tim</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/florian-lipowitz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tim-merlier/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Uijtdebroeks, Cian</t>
+          <t>Paret-Peintre, Valentin</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/valentin-paret-peintre/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -7318,23 +7454,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Vauquelin, Kévin</t>
+          <t>Kanter, Max</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/max-kanter/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>XAT</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -7352,57 +7488,57 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Arensman, Thymen</t>
+          <t>Oliveira, Nelson</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/nelson-oliveira/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Foss, Tobias</t>
+          <t>Uijtdebroeks, Cian</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tobias-foss/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -7420,318 +7556,339 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Wellens, Tim</t>
+          <t>Vauquelin, Kévin</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tim-wellens/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>UAD</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Arensman, Thymen</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Foss, Tobias</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/tobias-foss/2026</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Wellens, Tim</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/tim-wellens/2026</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>UAD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>55.6</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>History (eerdere jaren)</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>general_winner</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>points_winner</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>mountain_winner</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>youth_winner</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Pan y aqua</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Belahu</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Yellow bitch</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>SexySeixas</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Not Kermit</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Plak-bidon</t>
+          <t>Not Kermit</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>Belahu</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tour d'Hans</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>vlammie</t>
+          <t>Not Kermit</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tour d'Hans</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Plak-bidon</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Not Kermit</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Chi’s cycling</t>
+          <t>Tour d'Hans</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>vlammie</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7741,51 +7898,51 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Tour d'Hans</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ga-toch-fietsuh</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>Pan y aqua</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Ga-toch-fietsuh</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Ko-fidis</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7795,12 +7952,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Chi’s cycling</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7812,25 +7969,106 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Not Kermit</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Ga-toch-fietsuh</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Ga-toch-fietsuh</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>The O Team</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Pan y aqua</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>The O Team</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>Ko-fidis</t>
         </is>

--- a/data/dashboard.xlsx
+++ b/data/dashboard.xlsx
@@ -209,12 +209,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -277,12 +277,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -311,12 +311,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -379,12 +379,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -413,12 +413,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -447,12 +447,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -481,12 +481,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$4</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -602,12 +602,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$4</f>
+              <f>'Verloop GC-punten'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$B$2:$B$4</f>
+              <f>'Verloop GC-punten'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -636,12 +636,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$4</f>
+              <f>'Verloop GC-punten'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$C$2:$C$4</f>
+              <f>'Verloop GC-punten'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -670,12 +670,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$4</f>
+              <f>'Verloop GC-punten'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$D$2:$D$4</f>
+              <f>'Verloop GC-punten'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -704,12 +704,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$4</f>
+              <f>'Verloop GC-punten'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$E$2:$E$4</f>
+              <f>'Verloop GC-punten'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -738,12 +738,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$4</f>
+              <f>'Verloop GC-punten'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$F$2:$F$4</f>
+              <f>'Verloop GC-punten'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$4</f>
+              <f>'Verloop GC-punten'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$G$2:$G$4</f>
+              <f>'Verloop GC-punten'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -806,12 +806,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$4</f>
+              <f>'Verloop GC-punten'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$H$2:$H$4</f>
+              <f>'Verloop GC-punten'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -840,12 +840,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$4</f>
+              <f>'Verloop GC-punten'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$I$2:$I$4</f>
+              <f>'Verloop GC-punten'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -874,12 +874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$4</f>
+              <f>'Verloop GC-punten'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$J$2:$J$4</f>
+              <f>'Verloop GC-punten'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -995,12 +995,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$B$2:$B$4</f>
+              <f>'Verloop Puntenklassement'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -1029,12 +1029,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$C$2:$C$4</f>
+              <f>'Verloop Puntenklassement'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1063,12 +1063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$D$2:$D$4</f>
+              <f>'Verloop Puntenklassement'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1097,12 +1097,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$E$2:$E$4</f>
+              <f>'Verloop Puntenklassement'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -1131,12 +1131,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$F$2:$F$4</f>
+              <f>'Verloop Puntenklassement'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -1165,12 +1165,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$G$2:$G$4</f>
+              <f>'Verloop Puntenklassement'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -1199,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$H$2:$H$4</f>
+              <f>'Verloop Puntenklassement'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -1233,12 +1233,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$I$2:$I$4</f>
+              <f>'Verloop Puntenklassement'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -1267,12 +1267,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$4</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$J$2:$J$4</f>
+              <f>'Verloop Puntenklassement'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -1388,12 +1388,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$B$2:$B$4</f>
+              <f>'Verloop Bergklassement'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -1422,12 +1422,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$C$2:$C$4</f>
+              <f>'Verloop Bergklassement'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1456,12 +1456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$D$2:$D$4</f>
+              <f>'Verloop Bergklassement'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1490,12 +1490,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$E$2:$E$4</f>
+              <f>'Verloop Bergklassement'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -1524,12 +1524,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$F$2:$F$4</f>
+              <f>'Verloop Bergklassement'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -1558,12 +1558,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$G$2:$G$4</f>
+              <f>'Verloop Bergklassement'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -1592,12 +1592,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$H$2:$H$4</f>
+              <f>'Verloop Bergklassement'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -1626,12 +1626,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$I$2:$I$4</f>
+              <f>'Verloop Bergklassement'!$I$2:$I$5</f>
             </numRef>
           </val>
         </ser>
@@ -1660,12 +1660,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$4</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$J$2:$J$4</f>
+              <f>'Verloop Bergklassement'!$J$2:$J$5</f>
             </numRef>
           </val>
         </ser>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>270</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>491</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>277</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>141</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>485</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2298,12 +2298,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>274</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2313,12 +2313,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>464</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2341,12 +2341,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>434</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2384,27 +2384,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>234</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>109</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>425</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -2427,27 +2427,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>234</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>424</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>384</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2513,32 +2513,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>212</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>89</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>369</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2556,32 +2556,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>197</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>365</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2663,22 +2663,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>143</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>277</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2696,7 +2696,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2706,19 +2706,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>20</t>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>274</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,7 +2739,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2749,22 +2749,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>270</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,7 +2782,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2792,24 +2792,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>77</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>-</t>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>234</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2825,7 +2825,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2835,22 +2835,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>104</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>234</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,7 +2868,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2878,22 +2878,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>216</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>212</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,7 +2954,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2964,22 +2964,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,7 +2997,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3007,22 +3007,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>197</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,7 +3094,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3137,7 +3137,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3180,7 +3180,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3223,7 +3223,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3266,7 +3266,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -3660,17 +3660,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -3688,12 +3688,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -3716,12 +3716,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -3744,12 +3744,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3949,6 +3949,40 @@
         <v>173</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Stage 4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C5" t="n">
+        <v>74</v>
+      </c>
+      <c r="D5" t="n">
+        <v>61</v>
+      </c>
+      <c r="E5" t="n">
+        <v>61</v>
+      </c>
+      <c r="F5" t="n">
+        <v>75</v>
+      </c>
+      <c r="G5" t="n">
+        <v>107</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" t="n">
+        <v>59</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3961,7 +3995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4130,6 +4164,40 @@
         <v>49</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Stage 4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4142,7 +4210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4284,6 +4352,37 @@
         <v>97</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Stage 4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>52</v>
+      </c>
+      <c r="C5" t="n">
+        <v>53</v>
+      </c>
+      <c r="D5" t="n">
+        <v>48</v>
+      </c>
+      <c r="E5" t="n">
+        <v>37</v>
+      </c>
+      <c r="F5" t="n">
+        <v>59</v>
+      </c>
+      <c r="G5" t="n">
+        <v>72</v>
+      </c>
+      <c r="H5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I5" t="n">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4296,7 +4395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4436,6 +4535,19 @@
       </c>
       <c r="J4" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Stage 4</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4498,33 +4610,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D5" t="n">
-        <v>-10</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>173</v>
+        <v>68</v>
       </c>
       <c r="D6" t="n">
-        <v>-11</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="7">
@@ -4534,109 +4646,109 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="D7" t="n">
-        <v>-12</v>
+        <v>-48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D8" t="n">
-        <v>-12</v>
+        <v>-55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="C9" t="n">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="D9" t="n">
-        <v>-19</v>
+        <v>-83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>74</v>
       </c>
       <c r="D10" t="n">
-        <v>-22</v>
+        <v>-87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>59</v>
       </c>
       <c r="D11" t="n">
-        <v>-23</v>
+        <v>-117</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C12" t="n">
-        <v>144</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>-24</v>
+        <v>-157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>-36</v>
+        <v>-159</v>
       </c>
     </row>
     <row r="16">
@@ -4671,65 +4783,65 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C18" t="n">
-        <v>189</v>
+        <v>107</v>
       </c>
       <c r="D18" t="n">
-        <v>129</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C19" t="n">
-        <v>176</v>
+        <v>74</v>
       </c>
       <c r="D19" t="n">
-        <v>123</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C20" t="n">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="D20" t="n">
-        <v>112</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>173</v>
+        <v>68</v>
       </c>
       <c r="D21" t="n">
-        <v>112</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -4742,74 +4854,74 @@
         <v>51</v>
       </c>
       <c r="C22" t="n">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="D22" t="n">
-        <v>93</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C23" t="n">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C24" t="n">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D24" t="n">
-        <v>69</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C25" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>65</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C26" t="n">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="D26" t="n">
-        <v>53</v>
+        <v>-45</v>
       </c>
     </row>
   </sheetData>
@@ -4823,7 +4935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4916,7 +5028,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>99</t>
         </is>
       </c>
     </row>
@@ -4950,7 +5062,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5164,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5266,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5538,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5878,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5980,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6184,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6286,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6762,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6830,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6970,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -6892,7 +7004,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -6910,91 +7022,91 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Del Toro, Isaac</t>
+          <t>Pedersen, Mads</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/isaac-del-toro/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mads-pedersen/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UAD</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Evenepoel, Remco</t>
+          <t>Del Toro, Isaac</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/remco-evenepoel/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/isaac-del-toro/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>UAD</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Seixas, Paul</t>
+          <t>Evenepoel, Remco</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/paul-seixas/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/remco-evenepoel/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DCT</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -7012,12 +7124,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ayuso, Juan</t>
+          <t>Simmons, Quinn</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/quinn-simmons/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7028,7 +7140,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -7046,12 +7158,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Pedersen, Mads</t>
+          <t>Vacek, Mathias</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mads-pedersen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mathias-vacek/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7062,120 +7174,120 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Carapaz, Richard</t>
+          <t>Seixas, Paul</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/paul-seixas/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>EFE</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Van Eetvelt, Lennert</t>
+          <t>Castrillo, Pablo</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/lennert-van-eetvelt/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/pablo-castrillo/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Lipowitz, Florian</t>
+          <t>Ayuso, Juan</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/florian-lipowitz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7310,7 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -7216,182 +7328,182 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Van Wilder, Ilan</t>
+          <t>Carapaz, Richard</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>EFE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Pidcock, Tom</t>
+          <t>Van Eetvelt, Lennert</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/lennert-van-eetvelt/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PQT</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ganna, Filippo</t>
+          <t>Philipsen, Jasper</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Philipsen, Jasper</t>
+          <t>Vauquelin, Kévin</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cort, Magnus</t>
+          <t>Lipowitz, Florian</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/magnus-cort-nielsen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/florian-lipowitz/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>UXM</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Merlier, Tim</t>
+          <t>Van Wilder, Ilan</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tim-merlier/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7402,109 +7514,109 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Paret-Peintre, Valentin</t>
+          <t>Pidcock, Tom</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/valentin-paret-peintre/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>PQT</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kanter, Max</t>
+          <t>Ganna, Filippo</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/max-kanter/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>XAT</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Oliveira, Nelson</t>
+          <t>Cort, Magnus</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/nelson-oliveira/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/magnus-cort-nielsen/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>UXM</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -7522,57 +7634,57 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Uijtdebroeks, Cian</t>
+          <t>Merlier, Tim</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tim-merlier/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Vauquelin, Kévin</t>
+          <t>Paret-Peintre, Valentin</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/valentin-paret-peintre/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -7590,57 +7702,57 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Arensman, Thymen</t>
+          <t>Denz, Nico</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/nico-denz/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Foss, Tobias</t>
+          <t>Kanter, Max</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tobias-foss/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/max-kanter/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>XAT</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -7658,279 +7770,307 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Wellens, Tim</t>
+          <t>Oliveira, Nelson</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tim-wellens/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/nelson-oliveira/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>UAD</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Uijtdebroeks, Cian</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Arensman, Thymen</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Foss, Tobias</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/tobias-foss/2026</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Wellens, Tim</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/tim-wellens/2026</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>UAD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>55.6</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>History (eerdere jaren)</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>general_winner</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>points_winner</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>mountain_winner</t>
         </is>
       </c>
-      <c r="E91" s="3" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>youth_winner</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Not_Kermit</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Pan y aqua</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Belahu</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Yellow bitch</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Pan y aqua</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Pan y aqua</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Pan y aqua</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Plak-bidon</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>SexySeixas</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Not Kermit</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tour d'Hans</t>
+          <t>Not Kermit</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>vlammie</t>
+          <t>Belahu</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tour d'Hans</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Not Kermit</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
           <t>Ko-fidis</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7942,88 +8082,88 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Chi’s cycling</t>
+          <t>Plak-bidon</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Not Kermit</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>Tour MondAIl</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
           <t>Bismarck</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
-        </is>
-      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Tour d'Hans</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>vlammie</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ga-toch-fietsuh</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Ga-toch-fietsuh</t>
+          <t>Tour d'Hans</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8043,32 +8183,140 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Chi’s cycling</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Not Kermit</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ga-toch-fietsuh</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Ga-toch-fietsuh</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>The O Team</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Pan y aqua</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>The O Team</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>Ko-fidis</t>
         </is>

--- a/data/dashboard.xlsx
+++ b/data/dashboard.xlsx
@@ -209,12 +209,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -277,12 +277,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -311,12 +311,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -379,12 +379,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -413,12 +413,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -447,12 +447,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -481,12 +481,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$5</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -602,12 +602,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$5</f>
+              <f>'Verloop GC-punten'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$B$2:$B$5</f>
+              <f>'Verloop GC-punten'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -636,12 +636,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$5</f>
+              <f>'Verloop GC-punten'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$C$2:$C$5</f>
+              <f>'Verloop GC-punten'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -670,12 +670,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$5</f>
+              <f>'Verloop GC-punten'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$D$2:$D$5</f>
+              <f>'Verloop GC-punten'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -704,12 +704,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$5</f>
+              <f>'Verloop GC-punten'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$E$2:$E$5</f>
+              <f>'Verloop GC-punten'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -738,12 +738,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$5</f>
+              <f>'Verloop GC-punten'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$F$2:$F$5</f>
+              <f>'Verloop GC-punten'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$5</f>
+              <f>'Verloop GC-punten'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$G$2:$G$5</f>
+              <f>'Verloop GC-punten'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -806,12 +806,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$5</f>
+              <f>'Verloop GC-punten'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$H$2:$H$5</f>
+              <f>'Verloop GC-punten'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -840,12 +840,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$5</f>
+              <f>'Verloop GC-punten'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$I$2:$I$5</f>
+              <f>'Verloop GC-punten'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -874,12 +874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$5</f>
+              <f>'Verloop GC-punten'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$J$2:$J$5</f>
+              <f>'Verloop GC-punten'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -995,12 +995,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$B$2:$B$5</f>
+              <f>'Verloop Puntenklassement'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -1029,12 +1029,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$C$2:$C$5</f>
+              <f>'Verloop Puntenklassement'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1063,12 +1063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$D$2:$D$5</f>
+              <f>'Verloop Puntenklassement'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -1097,12 +1097,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$E$2:$E$5</f>
+              <f>'Verloop Puntenklassement'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -1131,12 +1131,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$F$2:$F$5</f>
+              <f>'Verloop Puntenklassement'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -1165,12 +1165,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$G$2:$G$5</f>
+              <f>'Verloop Puntenklassement'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -1199,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$H$2:$H$5</f>
+              <f>'Verloop Puntenklassement'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -1233,12 +1233,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$I$2:$I$5</f>
+              <f>'Verloop Puntenklassement'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -1267,12 +1267,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$5</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$J$2:$J$5</f>
+              <f>'Verloop Puntenklassement'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -1388,12 +1388,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$B$2:$B$5</f>
+              <f>'Verloop Bergklassement'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -1422,12 +1422,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$C$2:$C$5</f>
+              <f>'Verloop Bergklassement'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1456,12 +1456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$D$2:$D$5</f>
+              <f>'Verloop Bergklassement'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -1490,12 +1490,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$E$2:$E$5</f>
+              <f>'Verloop Bergklassement'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -1524,12 +1524,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$F$2:$F$5</f>
+              <f>'Verloop Bergklassement'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -1558,12 +1558,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$G$2:$G$5</f>
+              <f>'Verloop Bergklassement'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -1592,12 +1592,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$H$2:$H$5</f>
+              <f>'Verloop Bergklassement'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -1626,12 +1626,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$I$2:$I$5</f>
+              <f>'Verloop Bergklassement'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -1660,12 +1660,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$5</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$J$2:$J$5</f>
+              <f>'Verloop Bergklassement'!$J$2:$J$7</f>
             </numRef>
           </val>
         </ser>
@@ -2217,22 +2217,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>513</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>161</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>947</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -2255,32 +2255,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>526</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>146</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>186</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2298,27 +2298,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>492</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>160</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>868</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2341,42 +2341,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>445</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>146</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>201</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2389,22 +2389,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>447</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>140</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>159</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>812</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -2427,27 +2427,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>167</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>204</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>789</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -2470,27 +2470,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>471</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>134</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>762</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2513,42 +2513,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>725</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2561,22 +2561,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>159</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>689</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2653,42 +2653,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>526</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2696,42 +2696,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>513</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,42 +2739,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>492</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,42 +2782,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>471</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,37 +2830,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>447</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,42 +2868,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>445</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2911,42 +2911,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>364</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,37 +2959,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>358</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,42 +2997,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>352</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,42 +3094,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>167</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3137,42 +3137,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3185,37 +3185,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3223,42 +3223,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3266,42 +3266,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3309,42 +3309,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -3352,42 +3352,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -3395,42 +3395,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -3438,42 +3438,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>91</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -3525,12 +3525,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -3553,12 +3553,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3576,17 +3576,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3604,17 +3604,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3983,6 +3983,74 @@
         <v>16</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Stage 5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>203</v>
+      </c>
+      <c r="C6" t="n">
+        <v>163</v>
+      </c>
+      <c r="D6" t="n">
+        <v>101</v>
+      </c>
+      <c r="E6" t="n">
+        <v>176</v>
+      </c>
+      <c r="F6" t="n">
+        <v>87</v>
+      </c>
+      <c r="G6" t="n">
+        <v>156</v>
+      </c>
+      <c r="H6" t="n">
+        <v>132</v>
+      </c>
+      <c r="I6" t="n">
+        <v>59</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Stage 6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>190</v>
+      </c>
+      <c r="C7" t="n">
+        <v>297</v>
+      </c>
+      <c r="D7" t="n">
+        <v>223</v>
+      </c>
+      <c r="E7" t="n">
+        <v>268</v>
+      </c>
+      <c r="F7" t="n">
+        <v>255</v>
+      </c>
+      <c r="G7" t="n">
+        <v>231</v>
+      </c>
+      <c r="H7" t="n">
+        <v>324</v>
+      </c>
+      <c r="I7" t="n">
+        <v>313</v>
+      </c>
+      <c r="J7" t="n">
+        <v>335</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3995,7 +4063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4198,6 +4266,74 @@
         <v>15</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Stage 5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>18</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Stage 6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>32</v>
+      </c>
+      <c r="C7" t="n">
+        <v>47</v>
+      </c>
+      <c r="D7" t="n">
+        <v>37</v>
+      </c>
+      <c r="E7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F7" t="n">
+        <v>34</v>
+      </c>
+      <c r="G7" t="n">
+        <v>32</v>
+      </c>
+      <c r="H7" t="n">
+        <v>49</v>
+      </c>
+      <c r="I7" t="n">
+        <v>48</v>
+      </c>
+      <c r="J7" t="n">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4210,7 +4346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4383,6 +4519,74 @@
         <v>38</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Stage 5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>189</v>
+      </c>
+      <c r="C6" t="n">
+        <v>145</v>
+      </c>
+      <c r="D6" t="n">
+        <v>89</v>
+      </c>
+      <c r="E6" t="n">
+        <v>163</v>
+      </c>
+      <c r="F6" t="n">
+        <v>78</v>
+      </c>
+      <c r="G6" t="n">
+        <v>137</v>
+      </c>
+      <c r="H6" t="n">
+        <v>122</v>
+      </c>
+      <c r="I6" t="n">
+        <v>46</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Stage 6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="n">
+        <v>107</v>
+      </c>
+      <c r="D7" t="n">
+        <v>78</v>
+      </c>
+      <c r="E7" t="n">
+        <v>95</v>
+      </c>
+      <c r="F7" t="n">
+        <v>80</v>
+      </c>
+      <c r="G7" t="n">
+        <v>76</v>
+      </c>
+      <c r="H7" t="n">
+        <v>121</v>
+      </c>
+      <c r="I7" t="n">
+        <v>122</v>
+      </c>
+      <c r="J7" t="n">
+        <v>124</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4395,7 +4599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4548,6 +4752,47 @@
       </c>
       <c r="G5" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Stage 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Stage 6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>75</v>
+      </c>
+      <c r="C7" t="n">
+        <v>130</v>
+      </c>
+      <c r="D7" t="n">
+        <v>98</v>
+      </c>
+      <c r="E7" t="n">
+        <v>120</v>
+      </c>
+      <c r="F7" t="n">
+        <v>128</v>
+      </c>
+      <c r="G7" t="n">
+        <v>110</v>
+      </c>
+      <c r="H7" t="n">
+        <v>141</v>
+      </c>
+      <c r="I7" t="n">
+        <v>130</v>
+      </c>
+      <c r="J7" t="n">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -4610,145 +4855,145 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>107</v>
+        <v>335</v>
       </c>
       <c r="D5" t="n">
-        <v>-18</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
-        <v>68</v>
+        <v>313</v>
       </c>
       <c r="D6" t="n">
-        <v>-42</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>75</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>-48</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>61</v>
+        <v>255</v>
       </c>
       <c r="D8" t="n">
-        <v>-55</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="C9" t="n">
-        <v>61</v>
+        <v>297</v>
       </c>
       <c r="D9" t="n">
-        <v>-83</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="C10" t="n">
-        <v>74</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>-87</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>176</v>
       </c>
       <c r="C11" t="n">
-        <v>59</v>
+        <v>268</v>
       </c>
       <c r="D11" t="n">
-        <v>-117</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c r="D12" t="n">
-        <v>-157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="D13" t="n">
-        <v>-159</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="16">
@@ -4783,65 +5028,65 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C18" t="n">
-        <v>107</v>
+        <v>335</v>
       </c>
       <c r="D18" t="n">
-        <v>51</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C19" t="n">
-        <v>74</v>
+        <v>324</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C20" t="n">
-        <v>75</v>
+        <v>313</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C21" t="n">
-        <v>68</v>
+        <v>297</v>
       </c>
       <c r="D21" t="n">
-        <v>23</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22">
@@ -4854,74 +5099,74 @@
         <v>51</v>
       </c>
       <c r="C22" t="n">
-        <v>61</v>
+        <v>268</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C23" t="n">
-        <v>59</v>
+        <v>255</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C24" t="n">
-        <v>61</v>
+        <v>231</v>
       </c>
       <c r="D24" t="n">
-        <v>-2</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C25" t="n">
-        <v>30</v>
+        <v>223</v>
       </c>
       <c r="D25" t="n">
-        <v>-30</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="D26" t="n">
-        <v>-45</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -4935,7 +5180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5028,7 +5273,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>189</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5307,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>146</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5341,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>79</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5375,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5409,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>73</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5443,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5477,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5511,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>112</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5545,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5579,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5681,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5749,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5783,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>132</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5817,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5851,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5885,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5953,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5987,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -5810,7 +6055,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -5878,7 +6123,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>77</t>
         </is>
       </c>
     </row>
@@ -5946,7 +6191,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -5980,7 +6225,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6259,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6327,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6361,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6497,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6633,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -6524,7 +6769,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6871,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -6762,7 +7007,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -6796,7 +7041,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -6970,7 +7215,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -7004,7 +7249,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -7038,7 +7283,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -7072,7 +7317,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -7106,7 +7351,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -7124,23 +7369,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Simmons, Quinn</t>
+          <t>Girmay, Biniam</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/quinn-simmons/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/biniam-girmay/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>NSN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -7158,57 +7403,57 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Vacek, Mathias</t>
+          <t>Seixas, Paul</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mathias-vacek/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/paul-seixas/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Seixas, Paul</t>
+          <t>Philipsen, Jasper</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/paul-seixas/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DCT</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -7226,23 +7471,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Castrillo, Pablo</t>
+          <t>Kanter, Max</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/pablo-castrillo/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/max-kanter/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>XAT</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -7260,12 +7505,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ayuso, Juan</t>
+          <t>Simmons, Quinn</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/quinn-simmons/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -7276,7 +7521,7 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -7294,23 +7539,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Girmay, Biniam</t>
+          <t>Ayuso, Juan</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/biniam-girmay/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NSN</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -7328,91 +7573,91 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Carapaz, Richard</t>
+          <t>Vacek, Mathias</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mathias-vacek/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>EFE</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Van Eetvelt, Lennert</t>
+          <t>Kooij, Olav</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/lennert-van-eetvelt/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/olav-kooij/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>44.4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Philipsen, Jasper</t>
+          <t>Merlier, Tim</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tim-merlier/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -7430,193 +7675,193 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Vauquelin, Kévin</t>
+          <t>Lipowitz, Florian</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/florian-lipowitz/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Lipowitz, Florian</t>
+          <t>Castrillo, Pablo</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/florian-lipowitz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/pablo-castrillo/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Van Wilder, Ilan</t>
+          <t>Carapaz, Richard</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>EFE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Pidcock, Tom</t>
+          <t>Van Eetvelt, Lennert</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/lennert-van-eetvelt/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PQT</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ganna, Filippo</t>
+          <t>Paret-Peintre, Valentin</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/valentin-paret-peintre/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cort, Magnus</t>
+          <t>Vauquelin, Kévin</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/magnus-cort-nielsen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UXM</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -7634,57 +7879,57 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Merlier, Tim</t>
+          <t>Fretin, Milan</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tim-merlier/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/milan-fretin/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Paret-Peintre, Valentin</t>
+          <t>Berckmoes, Jenno</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/valentin-paret-peintre/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jenno-berckmoes/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -7702,125 +7947,125 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Denz, Nico</t>
+          <t>Ackermann, Pascal</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/nico-denz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/pascal-ackermann/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>JAY</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kanter, Max</t>
+          <t>Campenaerts, Victor</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/max-kanter/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/victor-campenaerts/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>XAT</t>
+          <t>TVL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Oliveira, Nelson</t>
+          <t>Pidcock, Tom</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/nelson-oliveira/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>PQT</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Uijtdebroeks, Cian</t>
+          <t>Van Wilder, Ilan</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -7838,485 +8083,825 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Arensman, Thymen</t>
+          <t>Teunissen, Mike</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mike-teunissen/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>XAT</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Foss, Tobias</t>
+          <t>Wellens, Tim</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tobias-foss/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tim-wellens/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>UAD</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Wellens, Tim</t>
+          <t>Ganna, Filippo</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tim-wellens/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>UAD</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>22.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Cort, Magnus</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/magnus-cort-nielsen/2026</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>UXM</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Bauhaus, Phil</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/phil-bauhaus/2026</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TBV</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>History (eerdere jaren)</t>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>O'Connor, Ben</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/ben-o-connor/2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>JAY</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>general_winner</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>points_winner</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>mountain_winner</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>youth_winner</t>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Denz, Nico</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/nico-denz/2026</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>RBH</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Oliveira, Nelson</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>https://www.worldcyclingstats.com/en/rider/nelson-oliveira/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Alaphilippe, Julian</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>https://www.worldcyclingstats.com/en/rider/julian-alaphilippe/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
-        </is>
-      </c>
+          <t>TUD</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Uijtdebroeks, Cian</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Yellow bitch</t>
-        </is>
-      </c>
+          <t>MOV</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>Arensman, Thymen</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Pan y aqua</t>
-        </is>
-      </c>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>Baarle, Dylan van</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>https://www.worldcyclingstats.com/en/rider/dylan-van-baarle/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Plak-bidon</t>
-        </is>
-      </c>
+          <t>SOQ</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Foss, Tobias</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tobias-foss/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Tour d'Hans</t>
-        </is>
-      </c>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>vlammie</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Tour d'Hans</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Tour MondAIl</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Belahu</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Pan y aqua</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Belahu</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Chi’s cycling</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>History (eerdere jaren)</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Belahu</t>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>general_winner</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>points_winner</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>mountain_winner</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>youth_winner</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ga-toch-fietsuh</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Ga-toch-fietsuh</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>SexySeixas</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Not Kermit</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t>Not Kermit</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>Belahu</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SexySeixas</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SexySeixas</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Yellow bitch</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Not Kermit</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Plak-bidon</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Not Kermit</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Tour MondAIl</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Tour d'Hans</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>vlammie</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Tour d'Hans</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Tour MondAIl</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Chi’s cycling</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Not Kermit</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Ga-toch-fietsuh</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Ga-toch-fietsuh</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>The O Team</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>Pan y aqua</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>The O Team</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>Ko-fidis</t>
         </is>

--- a/data/dashboard.xlsx
+++ b/data/dashboard.xlsx
@@ -209,12 +209,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -277,12 +277,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -311,12 +311,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$8</f>
             </numRef>
           </val>
         </ser>
@@ -379,12 +379,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$8</f>
             </numRef>
           </val>
         </ser>
@@ -413,12 +413,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$8</f>
             </numRef>
           </val>
         </ser>
@@ -447,12 +447,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$8</f>
             </numRef>
           </val>
         </ser>
@@ -481,12 +481,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$7</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$8</f>
             </numRef>
           </val>
         </ser>
@@ -602,12 +602,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$7</f>
+              <f>'Verloop GC-punten'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$B$2:$B$7</f>
+              <f>'Verloop GC-punten'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -636,12 +636,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$7</f>
+              <f>'Verloop GC-punten'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$C$2:$C$7</f>
+              <f>'Verloop GC-punten'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -670,12 +670,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$7</f>
+              <f>'Verloop GC-punten'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$D$2:$D$7</f>
+              <f>'Verloop GC-punten'!$D$2:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -704,12 +704,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$7</f>
+              <f>'Verloop GC-punten'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$E$2:$E$7</f>
+              <f>'Verloop GC-punten'!$E$2:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -738,12 +738,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$7</f>
+              <f>'Verloop GC-punten'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$F$2:$F$7</f>
+              <f>'Verloop GC-punten'!$F$2:$F$8</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$7</f>
+              <f>'Verloop GC-punten'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$G$2:$G$7</f>
+              <f>'Verloop GC-punten'!$G$2:$G$8</f>
             </numRef>
           </val>
         </ser>
@@ -806,12 +806,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$7</f>
+              <f>'Verloop GC-punten'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$H$2:$H$7</f>
+              <f>'Verloop GC-punten'!$H$2:$H$8</f>
             </numRef>
           </val>
         </ser>
@@ -840,12 +840,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$7</f>
+              <f>'Verloop GC-punten'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$I$2:$I$7</f>
+              <f>'Verloop GC-punten'!$I$2:$I$8</f>
             </numRef>
           </val>
         </ser>
@@ -874,12 +874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$7</f>
+              <f>'Verloop GC-punten'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$J$2:$J$7</f>
+              <f>'Verloop GC-punten'!$J$2:$J$8</f>
             </numRef>
           </val>
         </ser>
@@ -995,12 +995,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$B$2:$B$7</f>
+              <f>'Verloop Puntenklassement'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -1029,12 +1029,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$C$2:$C$7</f>
+              <f>'Verloop Puntenklassement'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -1063,12 +1063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$D$2:$D$7</f>
+              <f>'Verloop Puntenklassement'!$D$2:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -1097,12 +1097,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$E$2:$E$7</f>
+              <f>'Verloop Puntenklassement'!$E$2:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -1131,12 +1131,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$F$2:$F$7</f>
+              <f>'Verloop Puntenklassement'!$F$2:$F$8</f>
             </numRef>
           </val>
         </ser>
@@ -1165,12 +1165,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$G$2:$G$7</f>
+              <f>'Verloop Puntenklassement'!$G$2:$G$8</f>
             </numRef>
           </val>
         </ser>
@@ -1199,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$H$2:$H$7</f>
+              <f>'Verloop Puntenklassement'!$H$2:$H$8</f>
             </numRef>
           </val>
         </ser>
@@ -1233,12 +1233,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$I$2:$I$7</f>
+              <f>'Verloop Puntenklassement'!$I$2:$I$8</f>
             </numRef>
           </val>
         </ser>
@@ -1267,12 +1267,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$7</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$J$2:$J$7</f>
+              <f>'Verloop Puntenklassement'!$J$2:$J$8</f>
             </numRef>
           </val>
         </ser>
@@ -1388,12 +1388,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$B$2:$B$7</f>
+              <f>'Verloop Bergklassement'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -1422,12 +1422,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$C$2:$C$7</f>
+              <f>'Verloop Bergklassement'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -1456,12 +1456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$D$2:$D$7</f>
+              <f>'Verloop Bergklassement'!$D$2:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -1490,12 +1490,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$E$2:$E$7</f>
+              <f>'Verloop Bergklassement'!$E$2:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -1524,12 +1524,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$F$2:$F$7</f>
+              <f>'Verloop Bergklassement'!$F$2:$F$8</f>
             </numRef>
           </val>
         </ser>
@@ -1558,12 +1558,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$G$2:$G$7</f>
+              <f>'Verloop Bergklassement'!$G$2:$G$8</f>
             </numRef>
           </val>
         </ser>
@@ -1592,12 +1592,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$H$2:$H$7</f>
+              <f>'Verloop Bergklassement'!$H$2:$H$8</f>
             </numRef>
           </val>
         </ser>
@@ -1626,12 +1626,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$I$2:$I$7</f>
+              <f>'Verloop Bergklassement'!$I$2:$I$8</f>
             </numRef>
           </val>
         </ser>
@@ -1660,12 +1660,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$7</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$J$2:$J$7</f>
+              <f>'Verloop Bergklassement'!$J$2:$J$8</f>
             </numRef>
           </val>
         </ser>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>639</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>642</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>235</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>610</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2313,12 +2313,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>199</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2341,32 +2341,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>634</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>166</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>960</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>541</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>191</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>941</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -2427,42 +2427,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>475</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>936</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -2470,42 +2470,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>437</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>184</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>841</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2513,32 +2513,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>167</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>838</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>442</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>195</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>805</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2673,12 +2673,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>642</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>205</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>639</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,32 +2739,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>634</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,32 +2782,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>211</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>141</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>610</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>179</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>541</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>475</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>442</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>437</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3525,12 +3525,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4051,6 +4051,40 @@
         <v>335</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Stage 7</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>198</v>
+      </c>
+      <c r="C8" t="n">
+        <v>168</v>
+      </c>
+      <c r="D8" t="n">
+        <v>116</v>
+      </c>
+      <c r="E8" t="n">
+        <v>160</v>
+      </c>
+      <c r="F8" t="n">
+        <v>116</v>
+      </c>
+      <c r="G8" t="n">
+        <v>129</v>
+      </c>
+      <c r="H8" t="n">
+        <v>178</v>
+      </c>
+      <c r="I8" t="n">
+        <v>80</v>
+      </c>
+      <c r="J8" t="n">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4063,7 +4097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4334,6 +4368,40 @@
         <v>47</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Stage 7</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>32</v>
+      </c>
+      <c r="C8" t="n">
+        <v>49</v>
+      </c>
+      <c r="D8" t="n">
+        <v>36</v>
+      </c>
+      <c r="E8" t="n">
+        <v>39</v>
+      </c>
+      <c r="F8" t="n">
+        <v>34</v>
+      </c>
+      <c r="G8" t="n">
+        <v>32</v>
+      </c>
+      <c r="H8" t="n">
+        <v>49</v>
+      </c>
+      <c r="I8" t="n">
+        <v>47</v>
+      </c>
+      <c r="J8" t="n">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4346,7 +4414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4587,6 +4655,37 @@
         <v>124</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Stage 7</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>163</v>
+      </c>
+      <c r="C8" t="n">
+        <v>116</v>
+      </c>
+      <c r="D8" t="n">
+        <v>78</v>
+      </c>
+      <c r="E8" t="n">
+        <v>118</v>
+      </c>
+      <c r="F8" t="n">
+        <v>79</v>
+      </c>
+      <c r="G8" t="n">
+        <v>94</v>
+      </c>
+      <c r="H8" t="n">
+        <v>126</v>
+      </c>
+      <c r="I8" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4599,7 +4698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4793,6 +4892,13 @@
       </c>
       <c r="J7" t="n">
         <v>151</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Stage 7</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4855,65 +4961,65 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="C5" t="n">
-        <v>335</v>
+        <v>198</v>
       </c>
       <c r="D5" t="n">
-        <v>315</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="C6" t="n">
-        <v>313</v>
+        <v>129</v>
       </c>
       <c r="D6" t="n">
-        <v>254</v>
+        <v>-102</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>223</v>
       </c>
       <c r="C7" t="n">
-        <v>324</v>
+        <v>116</v>
       </c>
       <c r="D7" t="n">
-        <v>192</v>
+        <v>-107</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>87</v>
+        <v>268</v>
       </c>
       <c r="C8" t="n">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="D8" t="n">
-        <v>168</v>
+        <v>-108</v>
       </c>
     </row>
     <row r="9">
@@ -4923,77 +5029,77 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>163</v>
+        <v>297</v>
       </c>
       <c r="C9" t="n">
-        <v>297</v>
+        <v>168</v>
       </c>
       <c r="D9" t="n">
-        <v>134</v>
+        <v>-129</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>255</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>116</v>
       </c>
       <c r="D10" t="n">
-        <v>122</v>
+        <v>-139</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>176</v>
+        <v>324</v>
       </c>
       <c r="C11" t="n">
-        <v>268</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>-146</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>156</v>
+        <v>313</v>
       </c>
       <c r="C12" t="n">
-        <v>231</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>75</v>
+        <v>-233</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>203</v>
+        <v>335</v>
       </c>
       <c r="C13" t="n">
-        <v>190</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>-13</v>
+        <v>-286</v>
       </c>
     </row>
     <row r="16">
@@ -5028,81 +5134,81 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C18" t="n">
-        <v>335</v>
+        <v>198</v>
       </c>
       <c r="D18" t="n">
-        <v>274</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C19" t="n">
-        <v>324</v>
+        <v>168</v>
       </c>
       <c r="D19" t="n">
-        <v>264</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C20" t="n">
-        <v>313</v>
+        <v>178</v>
       </c>
       <c r="D20" t="n">
-        <v>260</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C21" t="n">
-        <v>297</v>
+        <v>160</v>
       </c>
       <c r="D21" t="n">
-        <v>248</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C22" t="n">
-        <v>268</v>
+        <v>129</v>
       </c>
       <c r="D22" t="n">
-        <v>217</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
@@ -5115,58 +5221,58 @@
         <v>51</v>
       </c>
       <c r="C23" t="n">
-        <v>255</v>
+        <v>116</v>
       </c>
       <c r="D23" t="n">
-        <v>204</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C24" t="n">
-        <v>231</v>
+        <v>116</v>
       </c>
       <c r="D24" t="n">
-        <v>175</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>223</v>
+        <v>80</v>
       </c>
       <c r="D25" t="n">
-        <v>160</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="C26" t="n">
-        <v>190</v>
+        <v>49</v>
       </c>
       <c r="D26" t="n">
-        <v>145</v>
+        <v>-12</v>
       </c>
     </row>
   </sheetData>
@@ -5180,7 +5286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5273,7 +5379,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>204</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5413,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>158</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5447,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>83</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5481,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>87</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5515,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>106</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5549,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5617,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>121</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5685,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5719,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5889,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>167</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5957,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5991,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -5953,7 +6059,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -6055,7 +6161,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6229,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6467,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6739,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>109</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6977,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -7215,7 +7321,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -7233,68 +7339,68 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Vingegaard, Jonas</t>
+          <t>Pedersen, Mads</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/jonas-vingegaard-rasmussen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mads-pedersen/2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TVL</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pedersen, Mads</t>
+          <t>Vingegaard, Jonas</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mads-pedersen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jonas-vingegaard-rasmussen/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>TVL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>88.9</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7423,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -7335,91 +7441,91 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Evenepoel, Remco</t>
+          <t>Girmay, Biniam</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/remco-evenepoel/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/biniam-girmay/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>NSN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>119</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Girmay, Biniam</t>
+          <t>Kanter, Max</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/biniam-girmay/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/max-kanter/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NSN</t>
+          <t>XAT</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Seixas, Paul</t>
+          <t>Philipsen, Jasper</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/paul-seixas/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DCT</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -7437,23 +7543,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Philipsen, Jasper</t>
+          <t>Merlier, Tim</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tim-merlier/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -7471,68 +7577,68 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kanter, Max</t>
+          <t>Evenepoel, Remco</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/max-kanter/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/remco-evenepoel/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>XAT</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Simmons, Quinn</t>
+          <t>Seixas, Paul</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/quinn-simmons/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/paul-seixas/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7661,7 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -7573,12 +7679,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Vacek, Mathias</t>
+          <t>Simmons, Quinn</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mathias-vacek/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/quinn-simmons/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7589,86 +7695,86 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kooij, Olav</t>
+          <t>Vacek, Mathias</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/olav-kooij/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mathias-vacek/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DCT</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Merlier, Tim</t>
+          <t>Kooij, Olav</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tim-merlier/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/olav-kooij/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>44.4</t>
         </is>
       </c>
     </row>
@@ -7709,91 +7815,91 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Castrillo, Pablo</t>
+          <t>Fretin, Milan</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/pablo-castrillo/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/milan-fretin/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Carapaz, Richard</t>
+          <t>Castrillo, Pablo</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/pablo-castrillo/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>EFE</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Van Eetvelt, Lennert</t>
+          <t>Ackermann, Pascal</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/lennert-van-eetvelt/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/pascal-ackermann/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>JAY</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -7811,57 +7917,57 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Paret-Peintre, Valentin</t>
+          <t>Bauhaus, Phil</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/valentin-paret-peintre/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/phil-bauhaus/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>TBV</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Vauquelin, Kévin</t>
+          <t>Berckmoes, Jenno</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jenno-berckmoes/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -7879,46 +7985,46 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Fretin, Milan</t>
+          <t>Carapaz, Richard</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/milan-fretin/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>EFE</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Berckmoes, Jenno</t>
+          <t>Van Eetvelt, Lennert</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/jenno-berckmoes/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/lennert-van-eetvelt/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7929,137 +8035,137 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ackermann, Pascal</t>
+          <t>Paret-Peintre, Valentin</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/pascal-ackermann/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/valentin-paret-peintre/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JAY</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Campenaerts, Victor</t>
+          <t>Vauquelin, Kévin</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/victor-campenaerts/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TVL</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Pidcock, Tom</t>
+          <t>Teunissen, Mike</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mike-teunissen/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PQT</t>
+          <t>XAT</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Van Wilder, Ilan</t>
+          <t>Campenaerts, Victor</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/victor-campenaerts/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>TVL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -8071,182 +8177,182 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Teunissen, Mike</t>
+          <t>Pidcock, Tom</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mike-teunissen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>XAT</t>
+          <t>PQT</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Wellens, Tim</t>
+          <t>Van Wilder, Ilan</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tim-wellens/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UAD</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Ganna, Filippo</t>
+          <t>Wellens, Tim</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tim-wellens/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>UAD</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cort, Magnus</t>
+          <t>Ganna, Filippo</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/magnus-cort-nielsen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>UXM</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Bauhaus, Phil</t>
+          <t>Cort, Magnus</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/phil-bauhaus/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/magnus-cort-nielsen/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TBV</t>
+          <t>UXM</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
@@ -8423,51 +8529,51 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Arensman, Thymen</t>
+          <t>Poel, Mathieu van der</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mathieu-van-der-poel/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>44.4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Baarle, Dylan van</t>
+          <t>Arensman, Thymen</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/dylan-van-baarle/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -8479,29 +8585,29 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Foss, Tobias</t>
+          <t>Baarle, Dylan van</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tobias-foss/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/dylan-van-baarle/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -8522,184 +8628,191 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Foss, Tobias</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/tobias-foss/2026</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t>History (eerdere jaren)</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>general_winner</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>points_winner</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>mountain_winner</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>youth_winner</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Belahu</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Yellow bitch</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>SexySeixas</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Not Kermit</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Not Kermit</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>Belahu</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Not Kermit</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Plak-bidon</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8709,31 +8822,31 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Tour d'Hans</t>
+          <t>Plak-bidon</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>vlammie</t>
+          <t>Not Kermit</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>Tour MondAIl</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
           <t>Bismarck</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
       <c r="D112" t="inlineStr">
         <is>
           <t>Tour d'Hans</t>
@@ -8741,41 +8854,41 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>vlammie</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Tour d'Hans</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8785,123 +8898,150 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
           <t>Belahu</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Chi’s cycling</t>
-        </is>
-      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Chi’s cycling</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Belahu</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ga-toch-fietsuh</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Not Kermit</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Ga-toch-fietsuh</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Belahu</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>Ga-toch-fietsuh</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Ga-toch-fietsuh</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Belahu</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>The O Team</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>Pan y aqua</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>The O Team</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>Ko-fidis</t>
         </is>

--- a/data/dashboard.xlsx
+++ b/data/dashboard.xlsx
@@ -209,12 +209,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -277,12 +277,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -311,12 +311,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -379,12 +379,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$10</f>
             </numRef>
           </val>
         </ser>
@@ -413,12 +413,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$10</f>
             </numRef>
           </val>
         </ser>
@@ -447,12 +447,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$10</f>
             </numRef>
           </val>
         </ser>
@@ -481,12 +481,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$8</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$10</f>
             </numRef>
           </val>
         </ser>
@@ -602,12 +602,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$8</f>
+              <f>'Verloop GC-punten'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$B$2:$B$8</f>
+              <f>'Verloop GC-punten'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -636,12 +636,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$8</f>
+              <f>'Verloop GC-punten'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$C$2:$C$8</f>
+              <f>'Verloop GC-punten'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -670,12 +670,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$8</f>
+              <f>'Verloop GC-punten'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$D$2:$D$8</f>
+              <f>'Verloop GC-punten'!$D$2:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -704,12 +704,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$8</f>
+              <f>'Verloop GC-punten'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$E$2:$E$8</f>
+              <f>'Verloop GC-punten'!$E$2:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -738,12 +738,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$8</f>
+              <f>'Verloop GC-punten'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$F$2:$F$8</f>
+              <f>'Verloop GC-punten'!$F$2:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$8</f>
+              <f>'Verloop GC-punten'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$G$2:$G$8</f>
+              <f>'Verloop GC-punten'!$G$2:$G$10</f>
             </numRef>
           </val>
         </ser>
@@ -806,12 +806,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$8</f>
+              <f>'Verloop GC-punten'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$H$2:$H$8</f>
+              <f>'Verloop GC-punten'!$H$2:$H$10</f>
             </numRef>
           </val>
         </ser>
@@ -840,12 +840,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$8</f>
+              <f>'Verloop GC-punten'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$I$2:$I$8</f>
+              <f>'Verloop GC-punten'!$I$2:$I$10</f>
             </numRef>
           </val>
         </ser>
@@ -874,12 +874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$8</f>
+              <f>'Verloop GC-punten'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$J$2:$J$8</f>
+              <f>'Verloop GC-punten'!$J$2:$J$10</f>
             </numRef>
           </val>
         </ser>
@@ -995,12 +995,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$B$2:$B$8</f>
+              <f>'Verloop Puntenklassement'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -1029,12 +1029,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$C$2:$C$8</f>
+              <f>'Verloop Puntenklassement'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -1063,12 +1063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$D$2:$D$8</f>
+              <f>'Verloop Puntenklassement'!$D$2:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -1097,12 +1097,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$E$2:$E$8</f>
+              <f>'Verloop Puntenklassement'!$E$2:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -1131,12 +1131,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$F$2:$F$8</f>
+              <f>'Verloop Puntenklassement'!$F$2:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -1165,12 +1165,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$G$2:$G$8</f>
+              <f>'Verloop Puntenklassement'!$G$2:$G$10</f>
             </numRef>
           </val>
         </ser>
@@ -1199,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$H$2:$H$8</f>
+              <f>'Verloop Puntenklassement'!$H$2:$H$10</f>
             </numRef>
           </val>
         </ser>
@@ -1233,12 +1233,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$I$2:$I$8</f>
+              <f>'Verloop Puntenklassement'!$I$2:$I$10</f>
             </numRef>
           </val>
         </ser>
@@ -1267,12 +1267,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$8</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$J$2:$J$8</f>
+              <f>'Verloop Puntenklassement'!$J$2:$J$10</f>
             </numRef>
           </val>
         </ser>
@@ -1388,12 +1388,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$B$2:$B$8</f>
+              <f>'Verloop Bergklassement'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -1422,12 +1422,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$C$2:$C$8</f>
+              <f>'Verloop Bergklassement'!$C$2:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -1456,12 +1456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$D$2:$D$8</f>
+              <f>'Verloop Bergklassement'!$D$2:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -1490,12 +1490,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$E$2:$E$8</f>
+              <f>'Verloop Bergklassement'!$E$2:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -1524,12 +1524,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$F$2:$F$8</f>
+              <f>'Verloop Bergklassement'!$F$2:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -1558,12 +1558,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$G$2:$G$8</f>
+              <f>'Verloop Bergklassement'!$G$2:$G$10</f>
             </numRef>
           </val>
         </ser>
@@ -1592,12 +1592,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$H$2:$H$8</f>
+              <f>'Verloop Bergklassement'!$H$2:$H$10</f>
             </numRef>
           </val>
         </ser>
@@ -1626,12 +1626,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$I$2:$I$8</f>
+              <f>'Verloop Bergklassement'!$I$2:$I$10</f>
             </numRef>
           </val>
         </ser>
@@ -1660,12 +1660,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$8</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$J$2:$J$8</f>
+              <f>'Verloop Bergklassement'!$J$2:$J$10</f>
             </numRef>
           </val>
         </ser>
@@ -2212,27 +2212,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>895</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>334</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -2255,27 +2255,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>848</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>161</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>358</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2298,27 +2298,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>998</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>235</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2341,27 +2341,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>858</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>277</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2389,22 +2389,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>813</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>177</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>630</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>177</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>341</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -2475,22 +2475,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>618</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>174</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2513,42 +2513,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>577</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2556,32 +2556,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>419</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>167</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>341</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2653,32 +2653,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>429</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>184</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>270</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>998</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2696,32 +2696,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>294</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>153</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>131</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>268</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>895</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,32 +2739,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>151</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>141</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>216</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>858</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,32 +2782,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>191</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>848</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,12 +2830,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>283</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>183</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>813</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>213</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>630</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2911,32 +2911,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>184</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>618</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,32 +2954,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>165</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>577</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>147</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>419</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,42 +3094,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>177</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3137,42 +3137,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>177</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3195,27 +3195,27 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3223,12 +3223,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>167</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3266,12 +3266,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3309,12 +3309,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -3352,12 +3352,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3377,17 +3377,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -3395,32 +3395,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3438,32 +3438,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -3525,12 +3525,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -3553,12 +3553,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4085,6 +4085,74 @@
         <v>49</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Stage 8</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>232</v>
+      </c>
+      <c r="C9" t="n">
+        <v>191</v>
+      </c>
+      <c r="D9" t="n">
+        <v>112</v>
+      </c>
+      <c r="E9" t="n">
+        <v>194</v>
+      </c>
+      <c r="F9" t="n">
+        <v>133</v>
+      </c>
+      <c r="G9" t="n">
+        <v>174</v>
+      </c>
+      <c r="H9" t="n">
+        <v>183</v>
+      </c>
+      <c r="I9" t="n">
+        <v>76</v>
+      </c>
+      <c r="J9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Stage 9</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>241</v>
+      </c>
+      <c r="C10" t="n">
+        <v>182</v>
+      </c>
+      <c r="D10" t="n">
+        <v>105</v>
+      </c>
+      <c r="E10" t="n">
+        <v>149</v>
+      </c>
+      <c r="F10" t="n">
+        <v>157</v>
+      </c>
+      <c r="G10" t="n">
+        <v>216</v>
+      </c>
+      <c r="H10" t="n">
+        <v>141</v>
+      </c>
+      <c r="I10" t="n">
+        <v>216</v>
+      </c>
+      <c r="J10" t="n">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4097,7 +4165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4402,6 +4470,74 @@
         <v>46</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Stage 8</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="n">
+        <v>36</v>
+      </c>
+      <c r="E9" t="n">
+        <v>40</v>
+      </c>
+      <c r="F9" t="n">
+        <v>37</v>
+      </c>
+      <c r="G9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H9" t="n">
+        <v>52</v>
+      </c>
+      <c r="I9" t="n">
+        <v>47</v>
+      </c>
+      <c r="J9" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Stage 9</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>34</v>
+      </c>
+      <c r="C10" t="n">
+        <v>49</v>
+      </c>
+      <c r="D10" t="n">
+        <v>37</v>
+      </c>
+      <c r="E10" t="n">
+        <v>38</v>
+      </c>
+      <c r="F10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G10" t="n">
+        <v>33</v>
+      </c>
+      <c r="H10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I10" t="n">
+        <v>46</v>
+      </c>
+      <c r="J10" t="n">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4414,7 +4550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4686,6 +4822,74 @@
         <v>30</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Stage 8</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>194</v>
+      </c>
+      <c r="C9" t="n">
+        <v>138</v>
+      </c>
+      <c r="D9" t="n">
+        <v>74</v>
+      </c>
+      <c r="E9" t="n">
+        <v>151</v>
+      </c>
+      <c r="F9" t="n">
+        <v>93</v>
+      </c>
+      <c r="G9" t="n">
+        <v>136</v>
+      </c>
+      <c r="H9" t="n">
+        <v>128</v>
+      </c>
+      <c r="I9" t="n">
+        <v>26</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Stage 9</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>170</v>
+      </c>
+      <c r="C10" t="n">
+        <v>115</v>
+      </c>
+      <c r="D10" t="n">
+        <v>61</v>
+      </c>
+      <c r="E10" t="n">
+        <v>97</v>
+      </c>
+      <c r="F10" t="n">
+        <v>88</v>
+      </c>
+      <c r="G10" t="n">
+        <v>136</v>
+      </c>
+      <c r="H10" t="n">
+        <v>81</v>
+      </c>
+      <c r="I10" t="n">
+        <v>129</v>
+      </c>
+      <c r="J10" t="n">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4698,7 +4902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4899,6 +5103,38 @@
         <is>
           <t>Stage 7</t>
         </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Stage 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Stage 9</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>27</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22</v>
+      </c>
+      <c r="G10" t="n">
+        <v>37</v>
+      </c>
+      <c r="I10" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -4961,145 +5197,145 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>190</v>
+        <v>76</v>
       </c>
       <c r="C5" t="n">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>231</v>
+        <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D6" t="n">
-        <v>-102</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>223</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>116</v>
+        <v>216</v>
       </c>
       <c r="D7" t="n">
-        <v>-107</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>268</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D8" t="n">
-        <v>-108</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>297</v>
+        <v>232</v>
       </c>
       <c r="C9" t="n">
-        <v>168</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>-129</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>255</v>
+        <v>112</v>
       </c>
       <c r="C10" t="n">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D10" t="n">
-        <v>-139</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>324</v>
+        <v>191</v>
       </c>
       <c r="C11" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>-146</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>313</v>
+        <v>183</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>-233</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>335</v>
+        <v>194</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>149</v>
       </c>
       <c r="D13" t="n">
-        <v>-286</v>
+        <v>-45</v>
       </c>
     </row>
     <row r="16">
@@ -5138,93 +5374,93 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="C18" t="n">
-        <v>198</v>
+        <v>241</v>
       </c>
       <c r="D18" t="n">
-        <v>153</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="C19" t="n">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="D19" t="n">
-        <v>119</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="C20" t="n">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="D20" t="n">
-        <v>118</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>51</v>
+        <v>198</v>
       </c>
       <c r="C21" t="n">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="D21" t="n">
-        <v>109</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>56</v>
+        <v>180</v>
       </c>
       <c r="C22" t="n">
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="D22" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>51</v>
+        <v>168</v>
       </c>
       <c r="C23" t="n">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="24">
@@ -5234,45 +5470,45 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="C24" t="n">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D24" t="n">
-        <v>53</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>53</v>
+        <v>184</v>
       </c>
       <c r="C25" t="n">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="D25" t="n">
-        <v>27</v>
+        <v>-63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>61</v>
+        <v>212</v>
       </c>
       <c r="C26" t="n">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="D26" t="n">
-        <v>-12</v>
+        <v>-71</v>
       </c>
     </row>
   </sheetData>
@@ -5286,7 +5522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5379,7 +5615,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>250</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5649,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>184</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5683,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5717,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>138</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5751,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>159</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5785,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5853,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5887,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5921,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>76</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5955,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5989,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -5855,7 +6091,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -5889,7 +6125,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>231</t>
         </is>
       </c>
     </row>
@@ -5923,7 +6159,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>68</t>
         </is>
       </c>
     </row>
@@ -5957,7 +6193,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -5991,7 +6227,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6295,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6397,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6431,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6465,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>178</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6499,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6567,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6601,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6635,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6703,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6941,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6975,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>139</t>
         </is>
       </c>
     </row>
@@ -6875,7 +7111,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7349,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7485,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7557,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>250</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -7355,7 +7591,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>231</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -7389,7 +7625,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -7407,136 +7643,136 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Del Toro, Isaac</t>
+          <t>Girmay, Biniam</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/isaac-del-toro/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/biniam-girmay/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>UAD</t>
+          <t>NSN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Girmay, Biniam</t>
+          <t>Del Toro, Isaac</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/biniam-girmay/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/isaac-del-toro/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NSN</t>
+          <t>UAD</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kanter, Max</t>
+          <t>Philipsen, Jasper</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/max-kanter/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>XAT</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Philipsen, Jasper</t>
+          <t>Kanter, Max</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/max-kanter/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>XAT</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7795,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -7593,7 +7829,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -7627,7 +7863,7 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -7645,80 +7881,80 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ayuso, Juan</t>
+          <t>Kooij, Olav</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/olav-kooij/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>76</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>44.4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Simmons, Quinn</t>
+          <t>Pidcock, Tom</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/quinn-simmons/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>PQT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Vacek, Mathias</t>
+          <t>Simmons, Quinn</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mathias-vacek/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/quinn-simmons/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7729,86 +7965,86 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kooij, Olav</t>
+          <t>Ayuso, Juan</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/olav-kooij/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DCT</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Lipowitz, Florian</t>
+          <t>Vacek, Mathias</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/florian-lipowitz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mathias-vacek/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
@@ -7831,7 +8067,7 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -7849,34 +8085,34 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Castrillo, Pablo</t>
+          <t>Poel, Mathieu van der</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/pablo-castrillo/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mathieu-van-der-poel/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>44.4</t>
         </is>
       </c>
     </row>
@@ -7899,7 +8135,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -7917,34 +8153,34 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Bauhaus, Phil</t>
+          <t>Lipowitz, Florian</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/phil-bauhaus/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/florian-lipowitz/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TBV</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
@@ -7967,7 +8203,7 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -7985,34 +8221,34 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Carapaz, Richard</t>
+          <t>Bauhaus, Phil</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/phil-bauhaus/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>EFE</t>
+          <t>TBV</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8271,7 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -8053,23 +8289,23 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Paret-Peintre, Valentin</t>
+          <t>Castrillo, Pablo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/valentin-paret-peintre/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/pablo-castrillo/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -8087,23 +8323,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Vauquelin, Kévin</t>
+          <t>Paret-Peintre, Valentin</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/valentin-paret-peintre/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -8121,57 +8357,57 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Teunissen, Mike</t>
+          <t>Carapaz, Richard</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mike-teunissen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>XAT</t>
+          <t>EFE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Campenaerts, Victor</t>
+          <t>Ganna, Filippo</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/victor-campenaerts/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TVL</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -8189,57 +8425,57 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Pidcock, Tom</t>
+          <t>Vauquelin, Kévin</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PQT</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Van Wilder, Ilan</t>
+          <t>Teunissen, Mike</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mike-teunissen/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>XAT</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -8273,7 +8509,7 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -8291,23 +8527,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ganna, Filippo</t>
+          <t>Campenaerts, Victor</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/victor-campenaerts/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>TVL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -8325,23 +8561,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cort, Magnus</t>
+          <t>Van Wilder, Ilan</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/magnus-cort-nielsen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>UXM</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -8359,159 +8595,159 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>O'Connor, Ben</t>
+          <t>Cort, Magnus</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/ben-o-connor/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/magnus-cort-nielsen/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JAY</t>
+          <t>UXM</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Denz, Nico</t>
+          <t>Healy, Ben</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/nico-denz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ben-healy/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>EFE</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Oliveira, Nelson</t>
+          <t>O'Connor, Ben</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/nelson-oliveira/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ben-o-connor/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>JAY</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Alaphilippe, Julian</t>
+          <t>Aranburu, Álex</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/julian-alaphilippe/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/alex-aranburu/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TUD</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Uijtdebroeks, Cian</t>
+          <t>Denz, Nico</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/nico-denz/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -8529,125 +8765,125 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Poel, Mathieu van der</t>
+          <t>Oliveira, Nelson</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mathieu-van-der-poel/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/nelson-oliveira/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Arensman, Thymen</t>
+          <t>Van Gils, Maxim</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/maxim-van-gils/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>44.4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Baarle, Dylan van</t>
+          <t>Alaphilippe, Julian</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/dylan-van-baarle/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/julian-alaphilippe/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>TUD</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Foss, Tobias</t>
+          <t>Uijtdebroeks, Cian</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tobias-foss/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -8662,287 +8898,322 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Voisard, Yannis</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/yannis-voisard/2026</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>TUD</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Hirschi, Marc</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/marc-hirschi/2026</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>TUD</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+    </row>
     <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>History (eerdere jaren)</t>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Arensman, Thymen</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>general_winner</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>points_winner</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>mountain_winner</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>youth_winner</t>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Baarle, Dylan van</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/dylan-van-baarle/2026</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SOQ</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Foss, Tobias</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tobias-foss/2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Belahu</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Yellow bitch</t>
-        </is>
-      </c>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Pan y aqua</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Belahu</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Yellow bitch</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Pan y aqua</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Pan y aqua</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Pan y aqua</t>
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>History (eerdere jaren)</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Plak-bidon</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>general_winner</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>points_winner</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>mountain_winner</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>youth_winner</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Alegría</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
           <t>Tour MondAIl</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Tour d'Hans</t>
-        </is>
-      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>vlammie</t>
+          <t>SexySeixas</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Not Kermit</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tour d'Hans</t>
+          <t>Not Kermit</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Belahu</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Not Kermit</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
           <t>Ko-fidis</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Belahu</t>
-        </is>
-      </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Chi’s cycling</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8952,96 +9223,231 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Plak-bidon</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
           <t>Not Kermit</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Belahu</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ga-toch-fietsuh</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Ga-toch-fietsuh</t>
+          <t>Tour d'Hans</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>vlammie</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Tour d'Hans</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Chi’s cycling</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Not Kermit</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Ga-toch-fietsuh</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Ga-toch-fietsuh</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>The O Team</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Pan y aqua</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>The O Team</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>Ko-fidis</t>
         </is>

--- a/data/dashboard.xlsx
+++ b/data/dashboard.xlsx
@@ -209,12 +209,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -277,12 +277,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -311,12 +311,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$12</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -379,12 +379,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -413,12 +413,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$12</f>
             </numRef>
           </val>
         </ser>
@@ -447,12 +447,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$12</f>
             </numRef>
           </val>
         </ser>
@@ -481,12 +481,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$10</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$12</f>
             </numRef>
           </val>
         </ser>
@@ -602,12 +602,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$10</f>
+              <f>'Verloop GC-punten'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$B$2:$B$10</f>
+              <f>'Verloop GC-punten'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -636,12 +636,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$10</f>
+              <f>'Verloop GC-punten'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$C$2:$C$10</f>
+              <f>'Verloop GC-punten'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -670,12 +670,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$10</f>
+              <f>'Verloop GC-punten'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$D$2:$D$10</f>
+              <f>'Verloop GC-punten'!$D$2:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -704,12 +704,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$10</f>
+              <f>'Verloop GC-punten'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$E$2:$E$10</f>
+              <f>'Verloop GC-punten'!$E$2:$E$12</f>
             </numRef>
           </val>
         </ser>
@@ -738,12 +738,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$10</f>
+              <f>'Verloop GC-punten'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$F$2:$F$10</f>
+              <f>'Verloop GC-punten'!$F$2:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$10</f>
+              <f>'Verloop GC-punten'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$G$2:$G$10</f>
+              <f>'Verloop GC-punten'!$G$2:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -806,12 +806,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$10</f>
+              <f>'Verloop GC-punten'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$H$2:$H$10</f>
+              <f>'Verloop GC-punten'!$H$2:$H$12</f>
             </numRef>
           </val>
         </ser>
@@ -840,12 +840,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$10</f>
+              <f>'Verloop GC-punten'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$I$2:$I$10</f>
+              <f>'Verloop GC-punten'!$I$2:$I$12</f>
             </numRef>
           </val>
         </ser>
@@ -874,12 +874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$10</f>
+              <f>'Verloop GC-punten'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$J$2:$J$10</f>
+              <f>'Verloop GC-punten'!$J$2:$J$12</f>
             </numRef>
           </val>
         </ser>
@@ -995,12 +995,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$B$2:$B$10</f>
+              <f>'Verloop Puntenklassement'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -1029,12 +1029,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$C$2:$C$10</f>
+              <f>'Verloop Puntenklassement'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -1063,12 +1063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$D$2:$D$10</f>
+              <f>'Verloop Puntenklassement'!$D$2:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -1097,12 +1097,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$E$2:$E$10</f>
+              <f>'Verloop Puntenklassement'!$E$2:$E$12</f>
             </numRef>
           </val>
         </ser>
@@ -1131,12 +1131,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$F$2:$F$10</f>
+              <f>'Verloop Puntenklassement'!$F$2:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -1165,12 +1165,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$G$2:$G$10</f>
+              <f>'Verloop Puntenklassement'!$G$2:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -1199,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$H$2:$H$10</f>
+              <f>'Verloop Puntenklassement'!$H$2:$H$12</f>
             </numRef>
           </val>
         </ser>
@@ -1233,12 +1233,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$I$2:$I$10</f>
+              <f>'Verloop Puntenklassement'!$I$2:$I$12</f>
             </numRef>
           </val>
         </ser>
@@ -1267,12 +1267,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$10</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$J$2:$J$10</f>
+              <f>'Verloop Puntenklassement'!$J$2:$J$12</f>
             </numRef>
           </val>
         </ser>
@@ -1388,12 +1388,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$B$2:$B$10</f>
+              <f>'Verloop Bergklassement'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -1422,12 +1422,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$C$2:$C$10</f>
+              <f>'Verloop Bergklassement'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -1456,12 +1456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$D$2:$D$10</f>
+              <f>'Verloop Bergklassement'!$D$2:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -1490,12 +1490,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$E$2:$E$10</f>
+              <f>'Verloop Bergklassement'!$E$2:$E$12</f>
             </numRef>
           </val>
         </ser>
@@ -1524,12 +1524,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$F$2:$F$10</f>
+              <f>'Verloop Bergklassement'!$F$2:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -1558,12 +1558,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$G$2:$G$10</f>
+              <f>'Verloop Bergklassement'!$G$2:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -1592,12 +1592,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$H$2:$H$10</f>
+              <f>'Verloop Bergklassement'!$H$2:$H$12</f>
             </numRef>
           </val>
         </ser>
@@ -1626,12 +1626,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$I$2:$I$10</f>
+              <f>'Verloop Bergklassement'!$I$2:$I$12</f>
             </numRef>
           </val>
         </ser>
@@ -1660,12 +1660,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$10</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$J$2:$J$10</f>
+              <f>'Verloop Bergklassement'!$J$2:$J$12</f>
             </numRef>
           </val>
         </ser>
@@ -2212,27 +2212,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>272</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>466</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -2255,27 +2255,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>218</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>423</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2303,22 +2303,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>293</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2346,22 +2346,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>253</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>371</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2389,22 +2389,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>270</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>339</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>795</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>247</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>429</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -2475,22 +2475,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>779</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>254</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>338</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2518,22 +2518,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>756</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>207</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>353</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2561,37 +2561,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>585</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>433</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2658,12 +2658,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>553</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>244</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2673,12 +2673,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>331</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2701,12 +2701,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>225</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>330</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,32 +2739,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>394</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>292</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>191</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>173</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,32 +2782,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>398</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>251</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>141</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>277</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,12 +2830,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>264</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>244</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>319</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>795</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2916,12 +2916,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>221</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>225</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>214</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>779</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,22 +2959,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>211</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>252</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>756</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>275</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>585</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,34 +3094,34 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>-</t>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>272</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>270</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3190,17 +3190,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>254</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3223,42 +3223,42 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>253</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3266,42 +3266,42 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>247</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3309,32 +3309,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>243</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>218</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -3395,32 +3395,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>207</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -3438,42 +3438,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>191</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -3525,12 +3525,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -3553,12 +3553,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4153,6 +4153,74 @@
         <v>121</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Stage 10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>220</v>
+      </c>
+      <c r="C11" t="n">
+        <v>235</v>
+      </c>
+      <c r="D11" t="n">
+        <v>237</v>
+      </c>
+      <c r="E11" t="n">
+        <v>305</v>
+      </c>
+      <c r="F11" t="n">
+        <v>240</v>
+      </c>
+      <c r="G11" t="n">
+        <v>259</v>
+      </c>
+      <c r="H11" t="n">
+        <v>341</v>
+      </c>
+      <c r="I11" t="n">
+        <v>257</v>
+      </c>
+      <c r="J11" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Stage 11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>186</v>
+      </c>
+      <c r="C12" t="n">
+        <v>159</v>
+      </c>
+      <c r="D12" t="n">
+        <v>126</v>
+      </c>
+      <c r="E12" t="n">
+        <v>152</v>
+      </c>
+      <c r="F12" t="n">
+        <v>99</v>
+      </c>
+      <c r="G12" t="n">
+        <v>154</v>
+      </c>
+      <c r="H12" t="n">
+        <v>160</v>
+      </c>
+      <c r="I12" t="n">
+        <v>84</v>
+      </c>
+      <c r="J12" t="n">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4165,7 +4233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4538,6 +4606,74 @@
         <v>45</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Stage 10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>29</v>
+      </c>
+      <c r="C11" t="n">
+        <v>45</v>
+      </c>
+      <c r="D11" t="n">
+        <v>42</v>
+      </c>
+      <c r="E11" t="n">
+        <v>47</v>
+      </c>
+      <c r="F11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G11" t="n">
+        <v>40</v>
+      </c>
+      <c r="H11" t="n">
+        <v>54</v>
+      </c>
+      <c r="I11" t="n">
+        <v>44</v>
+      </c>
+      <c r="J11" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Stage 11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>29</v>
+      </c>
+      <c r="C12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D12" t="n">
+        <v>43</v>
+      </c>
+      <c r="E12" t="n">
+        <v>47</v>
+      </c>
+      <c r="F12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H12" t="n">
+        <v>54</v>
+      </c>
+      <c r="I12" t="n">
+        <v>44</v>
+      </c>
+      <c r="J12" t="n">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4550,7 +4686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4890,6 +5026,74 @@
         <v>66</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Stage 10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>104</v>
+      </c>
+      <c r="C11" t="n">
+        <v>112</v>
+      </c>
+      <c r="D11" t="n">
+        <v>99</v>
+      </c>
+      <c r="E11" t="n">
+        <v>145</v>
+      </c>
+      <c r="F11" t="n">
+        <v>106</v>
+      </c>
+      <c r="G11" t="n">
+        <v>112</v>
+      </c>
+      <c r="H11" t="n">
+        <v>162</v>
+      </c>
+      <c r="I11" t="n">
+        <v>129</v>
+      </c>
+      <c r="J11" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Stage 11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>153</v>
+      </c>
+      <c r="C12" t="n">
+        <v>111</v>
+      </c>
+      <c r="D12" t="n">
+        <v>80</v>
+      </c>
+      <c r="E12" t="n">
+        <v>101</v>
+      </c>
+      <c r="F12" t="n">
+        <v>55</v>
+      </c>
+      <c r="G12" t="n">
+        <v>110</v>
+      </c>
+      <c r="H12" t="n">
+        <v>102</v>
+      </c>
+      <c r="I12" t="n">
+        <v>36</v>
+      </c>
+      <c r="J12" t="n">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4902,7 +5106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5135,6 +5339,47 @@
       </c>
       <c r="I10" t="n">
         <v>31</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Stage 10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>73</v>
+      </c>
+      <c r="C11" t="n">
+        <v>64</v>
+      </c>
+      <c r="D11" t="n">
+        <v>89</v>
+      </c>
+      <c r="E11" t="n">
+        <v>99</v>
+      </c>
+      <c r="F11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G11" t="n">
+        <v>93</v>
+      </c>
+      <c r="H11" t="n">
+        <v>111</v>
+      </c>
+      <c r="I11" t="n">
+        <v>70</v>
+      </c>
+      <c r="J11" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Stage 11</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5197,33 +5442,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="C5" t="n">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="D5" t="n">
-        <v>140</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>235</v>
       </c>
       <c r="C6" t="n">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="D6" t="n">
-        <v>71</v>
+        <v>-76</v>
       </c>
     </row>
     <row r="7">
@@ -5233,77 +5478,77 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>174</v>
+        <v>259</v>
       </c>
       <c r="C7" t="n">
-        <v>216</v>
+        <v>154</v>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>-105</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>237</v>
       </c>
       <c r="C8" t="n">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>-111</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C9" t="n">
-        <v>241</v>
+        <v>99</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>-141</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112</v>
+        <v>305</v>
       </c>
       <c r="C10" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>-7</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>191</v>
+        <v>257</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>84</v>
       </c>
       <c r="D11" t="n">
-        <v>-9</v>
+        <v>-173</v>
       </c>
     </row>
     <row r="12">
@@ -5313,29 +5558,29 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>183</v>
+        <v>341</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>-42</v>
+        <v>-181</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>194</v>
+        <v>288</v>
       </c>
       <c r="C13" t="n">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>-45</v>
+        <v>-224</v>
       </c>
     </row>
     <row r="16">
@@ -5370,145 +5615,145 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>146</v>
+        <v>30</v>
       </c>
       <c r="C18" t="n">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="D18" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="C19" t="n">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="D19" t="n">
-        <v>79</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="C20" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="C21" t="n">
-        <v>216</v>
+        <v>159</v>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>180</v>
+        <v>61</v>
       </c>
       <c r="C22" t="n">
-        <v>182</v>
+        <v>126</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>168</v>
+        <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>-19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="C24" t="n">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="D24" t="n">
-        <v>-21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>184</v>
+        <v>59</v>
       </c>
       <c r="C25" t="n">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="D25" t="n">
-        <v>-63</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>212</v>
+        <v>75</v>
       </c>
       <c r="C26" t="n">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="D26" t="n">
-        <v>-71</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -5522,7 +5767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5615,7 +5860,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>337</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5894,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>238</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5928,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>140</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5962,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>156</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5996,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>212</t>
         </is>
       </c>
     </row>
@@ -5785,7 +6030,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -5819,7 +6064,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>78</t>
         </is>
       </c>
     </row>
@@ -5853,7 +6098,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -5887,7 +6132,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -5921,7 +6166,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>111</t>
         </is>
       </c>
     </row>
@@ -5955,7 +6200,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6268,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6336,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6370,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>279</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6404,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>80</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6438,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6472,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>96</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6540,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6642,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>84</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6710,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>226</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6812,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>69</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6948,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>53</t>
         </is>
       </c>
     </row>
@@ -6771,7 +7016,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -6839,7 +7084,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -6975,7 +7220,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>172</t>
         </is>
       </c>
     </row>
@@ -7077,7 +7322,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7356,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7458,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7492,7 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7594,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7628,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7662,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -7485,7 +7730,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7802,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>337</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -7591,7 +7836,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>279</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -7625,7 +7870,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>238</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -7659,7 +7904,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>226</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -7677,68 +7922,68 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Del Toro, Isaac</t>
+          <t>Philipsen, Jasper</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/isaac-del-toro/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>UAD</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Philipsen, Jasper</t>
+          <t>Del Toro, Isaac</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/isaac-del-toro/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>UAD</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>187</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
@@ -7761,7 +8006,7 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -7795,7 +8040,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -7829,7 +8074,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -7863,7 +8108,7 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -7897,7 +8142,7 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -7915,57 +8160,57 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Pidcock, Tom</t>
+          <t>Ayuso, Juan</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PQT</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Simmons, Quinn</t>
+          <t>Fretin, Milan</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/quinn-simmons/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/milan-fretin/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -7983,91 +8228,91 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ayuso, Juan</t>
+          <t>Pidcock, Tom</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>PQT</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Vacek, Mathias</t>
+          <t>Carapaz, Richard</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mathias-vacek/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>EFE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Fretin, Milan</t>
+          <t>Simmons, Quinn</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/milan-fretin/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/quinn-simmons/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -8101,7 +8346,7 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -8135,7 +8380,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -8169,7 +8414,7 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -8187,23 +8432,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Berckmoes, Jenno</t>
+          <t>Vacek, Mathias</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/jenno-berckmoes/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mathias-vacek/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -8221,46 +8466,46 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Bauhaus, Phil</t>
+          <t>Paret-Peintre, Valentin</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/phil-bauhaus/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/valentin-paret-peintre/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TBV</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Van Eetvelt, Lennert</t>
+          <t>Berckmoes, Jenno</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/lennert-van-eetvelt/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jenno-berckmoes/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -8271,75 +8516,75 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Castrillo, Pablo</t>
+          <t>Bauhaus, Phil</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/pablo-castrillo/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/phil-bauhaus/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>TBV</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Paret-Peintre, Valentin</t>
+          <t>Castrillo, Pablo</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/valentin-paret-peintre/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/pablo-castrillo/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -8357,34 +8602,34 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Carapaz, Richard</t>
+          <t>Van Eetvelt, Lennert</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/lennert-van-eetvelt/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>EFE</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8686,7 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -8475,7 +8720,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -8493,91 +8738,91 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Wellens, Tim</t>
+          <t>Van Wilder, Ilan</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tim-wellens/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>UAD</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Campenaerts, Victor</t>
+          <t>Wellens, Tim</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/victor-campenaerts/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tim-wellens/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TVL</t>
+          <t>UAD</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Van Wilder, Ilan</t>
+          <t>Oliveira, Nelson</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/nelson-oliveira/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -8595,91 +8840,91 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cort, Magnus</t>
+          <t>Alaphilippe, Julian</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/magnus-cort-nielsen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/julian-alaphilippe/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>UXM</t>
+          <t>TUD</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Healy, Ben</t>
+          <t>Cort, Magnus</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/ben-healy/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/magnus-cort-nielsen/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>EFE</t>
+          <t>UXM</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>O'Connor, Ben</t>
+          <t>Campenaerts, Victor</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/ben-o-connor/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/victor-campenaerts/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>JAY</t>
+          <t>TVL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -8697,91 +8942,91 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Aranburu, Álex</t>
+          <t>Healy, Ben</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/alex-aranburu/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ben-healy/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>EFE</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Denz, Nico</t>
+          <t>O'Connor, Ben</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/nico-denz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ben-o-connor/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>JAY</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Oliveira, Nelson</t>
+          <t>Tiberi, Antonio</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/nelson-oliveira/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/antonio-tiberi/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>TBV</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -8799,91 +9044,91 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Van Gils, Maxim</t>
+          <t>Voisard, Yannis</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/maxim-van-gils/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/yannis-voisard/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>TUD</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Alaphilippe, Julian</t>
+          <t>Aranburu, Álex</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/julian-alaphilippe/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/alex-aranburu/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TUD</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Uijtdebroeks, Cian</t>
+          <t>Denz, Nico</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/nico-denz/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -8901,57 +9146,57 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Voisard, Yannis</t>
+          <t>Van Gils, Maxim</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/yannis-voisard/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/maxim-van-gils/2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TUD</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>44.4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Hirschi, Marc</t>
+          <t>Uijtdebroeks, Cian</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/marc-hirschi/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TUD</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -8969,51 +9214,51 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Arensman, Thymen</t>
+          <t>Hirschi, Marc</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/marc-hirschi/2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>TUD</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Baarle, Dylan van</t>
+          <t>Arensman, Thymen</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/dylan-van-baarle/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -9025,29 +9270,29 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Foss, Tobias</t>
+          <t>Baarle, Dylan van</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tobias-foss/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/dylan-van-baarle/2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -9068,184 +9313,191 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Foss, Tobias</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://www.worldcyclingstats.com/en/rider/tobias-foss/2026</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>IGD</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
         <is>
           <t>History (eerdere jaren)</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
         <is>
           <t>general_winner</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>points_winner</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>mountain_winner</t>
         </is>
       </c>
-      <c r="E111" s="3" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>youth_winner</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Belahu</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Alegría</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Tour MondAIl</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>SexySeixas</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>SexySeixas</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Not Kermit</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Not Kermit</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>Belahu</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Not Kermit</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Plak-bidon</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Not Kermit</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -9255,31 +9507,31 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Tour d'Hans</t>
+          <t>Plak-bidon</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>vlammie</t>
+          <t>Not Kermit</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>Tour MondAIl</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
           <t>Bismarck</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
       <c r="D118" t="inlineStr">
         <is>
           <t>Tour d'Hans</t>
@@ -9287,41 +9539,41 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>vlammie</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Tour d'Hans</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9331,123 +9583,150 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
           <t>Belahu</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Chi’s cycling</t>
-        </is>
-      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bismarck</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Chi’s cycling</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
           <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Not Kermit</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Belahu</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ga-toch-fietsuh</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Not Kermit</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Ga-toch-fietsuh</t>
+          <t>Bismarck</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Belahu</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
+          <t>Ga-toch-fietsuh</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Pan y aqua</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Ga-toch-fietsuh</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
           <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Ko-fidis</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Belahu</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Bismarck</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ko-fidis</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Belahu</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Bismarck</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>The O Team</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Pan y aqua</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>The O Team</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>Ko-fidis</t>
         </is>

--- a/data/dashboard.xlsx
+++ b/data/dashboard.xlsx
@@ -209,12 +209,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -277,12 +277,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -311,12 +311,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -379,12 +379,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -413,12 +413,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -447,12 +447,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$13</f>
             </numRef>
           </val>
         </ser>
@@ -481,12 +481,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$12</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$13</f>
             </numRef>
           </val>
         </ser>
@@ -602,12 +602,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$12</f>
+              <f>'Verloop GC-punten'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$B$2:$B$12</f>
+              <f>'Verloop GC-punten'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -636,12 +636,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$12</f>
+              <f>'Verloop GC-punten'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$C$2:$C$12</f>
+              <f>'Verloop GC-punten'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -670,12 +670,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$12</f>
+              <f>'Verloop GC-punten'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$D$2:$D$12</f>
+              <f>'Verloop GC-punten'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -704,12 +704,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$12</f>
+              <f>'Verloop GC-punten'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$E$2:$E$12</f>
+              <f>'Verloop GC-punten'!$E$2:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -738,12 +738,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$12</f>
+              <f>'Verloop GC-punten'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$F$2:$F$12</f>
+              <f>'Verloop GC-punten'!$F$2:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$12</f>
+              <f>'Verloop GC-punten'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$G$2:$G$12</f>
+              <f>'Verloop GC-punten'!$G$2:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -806,12 +806,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$12</f>
+              <f>'Verloop GC-punten'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$H$2:$H$12</f>
+              <f>'Verloop GC-punten'!$H$2:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -840,12 +840,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$12</f>
+              <f>'Verloop GC-punten'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$I$2:$I$12</f>
+              <f>'Verloop GC-punten'!$I$2:$I$13</f>
             </numRef>
           </val>
         </ser>
@@ -874,12 +874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$12</f>
+              <f>'Verloop GC-punten'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$J$2:$J$12</f>
+              <f>'Verloop GC-punten'!$J$2:$J$13</f>
             </numRef>
           </val>
         </ser>
@@ -995,12 +995,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$B$2:$B$12</f>
+              <f>'Verloop Puntenklassement'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -1029,12 +1029,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$C$2:$C$12</f>
+              <f>'Verloop Puntenklassement'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -1063,12 +1063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$D$2:$D$12</f>
+              <f>'Verloop Puntenklassement'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -1097,12 +1097,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$E$2:$E$12</f>
+              <f>'Verloop Puntenklassement'!$E$2:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -1131,12 +1131,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$F$2:$F$12</f>
+              <f>'Verloop Puntenklassement'!$F$2:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -1165,12 +1165,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$G$2:$G$12</f>
+              <f>'Verloop Puntenklassement'!$G$2:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -1199,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$H$2:$H$12</f>
+              <f>'Verloop Puntenklassement'!$H$2:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -1233,12 +1233,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$I$2:$I$12</f>
+              <f>'Verloop Puntenklassement'!$I$2:$I$13</f>
             </numRef>
           </val>
         </ser>
@@ -1267,12 +1267,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$12</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$J$2:$J$12</f>
+              <f>'Verloop Puntenklassement'!$J$2:$J$13</f>
             </numRef>
           </val>
         </ser>
@@ -1388,12 +1388,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$B$2:$B$12</f>
+              <f>'Verloop Bergklassement'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -1422,12 +1422,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$C$2:$C$12</f>
+              <f>'Verloop Bergklassement'!$C$2:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -1456,12 +1456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$D$2:$D$12</f>
+              <f>'Verloop Bergklassement'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -1490,12 +1490,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$E$2:$E$12</f>
+              <f>'Verloop Bergklassement'!$E$2:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -1524,12 +1524,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$F$2:$F$12</f>
+              <f>'Verloop Bergklassement'!$F$2:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -1558,12 +1558,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$G$2:$G$12</f>
+              <f>'Verloop Bergklassement'!$G$2:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -1592,12 +1592,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$H$2:$H$12</f>
+              <f>'Verloop Bergklassement'!$H$2:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -1626,12 +1626,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$I$2:$I$12</f>
+              <f>'Verloop Bergklassement'!$I$2:$I$13</f>
             </numRef>
           </val>
         </ser>
@@ -1660,12 +1660,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$12</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$J$2:$J$12</f>
+              <f>'Verloop Bergklassement'!$J$2:$J$13</f>
             </numRef>
           </val>
         </ser>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>520</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -2255,27 +2255,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>322</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2298,27 +2298,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>218</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>467</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>418</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2389,22 +2389,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>274</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>379</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>836</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>473</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>889</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>378</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>847</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>396</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>596</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>479</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>706</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2673,12 +2673,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>370</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>58</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2696,32 +2696,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>528</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>251</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>141</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>313</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,32 +2739,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>476</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>225</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>131</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>366</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>69</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,32 +2782,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>496</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>292</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>191</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>466</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>279</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,32 +2868,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>302</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>225</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>889</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2911,32 +2911,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>272</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>181</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>282</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>847</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,32 +2954,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>836</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>596</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,42 +3094,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>274</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3137,32 +3137,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>272</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3525,12 +3525,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -3553,12 +3553,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4221,6 +4221,40 @@
         <v>64</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stage 12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>234</v>
+      </c>
+      <c r="C13" t="n">
+        <v>197</v>
+      </c>
+      <c r="D13" t="n">
+        <v>137</v>
+      </c>
+      <c r="E13" t="n">
+        <v>224</v>
+      </c>
+      <c r="F13" t="n">
+        <v>154</v>
+      </c>
+      <c r="G13" t="n">
+        <v>193</v>
+      </c>
+      <c r="H13" t="n">
+        <v>191</v>
+      </c>
+      <c r="I13" t="n">
+        <v>89</v>
+      </c>
+      <c r="J13" t="n">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4233,7 +4267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4674,6 +4708,40 @@
         <v>46</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stage 12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>29</v>
+      </c>
+      <c r="C13" t="n">
+        <v>44</v>
+      </c>
+      <c r="D13" t="n">
+        <v>43</v>
+      </c>
+      <c r="E13" t="n">
+        <v>47</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G13" t="n">
+        <v>40</v>
+      </c>
+      <c r="H13" t="n">
+        <v>54</v>
+      </c>
+      <c r="I13" t="n">
+        <v>44</v>
+      </c>
+      <c r="J13" t="n">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4686,7 +4754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5094,6 +5162,40 @@
         <v>14</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stage 12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>201</v>
+      </c>
+      <c r="C13" t="n">
+        <v>149</v>
+      </c>
+      <c r="D13" t="n">
+        <v>91</v>
+      </c>
+      <c r="E13" t="n">
+        <v>173</v>
+      </c>
+      <c r="F13" t="n">
+        <v>110</v>
+      </c>
+      <c r="G13" t="n">
+        <v>145</v>
+      </c>
+      <c r="H13" t="n">
+        <v>133</v>
+      </c>
+      <c r="I13" t="n">
+        <v>41</v>
+      </c>
+      <c r="J13" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5106,7 +5208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5380,6 +5482,16 @@
         <is>
           <t>Stage 11</t>
         </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stage 12</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5442,129 +5554,129 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>220</v>
+        <v>152</v>
       </c>
       <c r="C5" t="n">
-        <v>186</v>
+        <v>224</v>
       </c>
       <c r="D5" t="n">
-        <v>-34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>235</v>
+        <v>99</v>
       </c>
       <c r="C6" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D6" t="n">
-        <v>-76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>186</v>
       </c>
       <c r="C7" t="n">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="D7" t="n">
-        <v>-105</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="C8" t="n">
-        <v>126</v>
+        <v>193</v>
       </c>
       <c r="D8" t="n">
-        <v>-111</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>240</v>
+        <v>159</v>
       </c>
       <c r="C9" t="n">
-        <v>99</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>-141</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>305</v>
+        <v>160</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>-153</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>257</v>
+        <v>126</v>
       </c>
       <c r="C11" t="n">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>-173</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>341</v>
+        <v>84</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>-181</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -5574,13 +5686,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>288</v>
+        <v>64</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>-224</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="16">
@@ -5615,33 +5727,33 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="C18" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D18" t="n">
-        <v>130</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="C19" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D19" t="n">
-        <v>118</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -5651,109 +5763,109 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="C20" t="n">
-        <v>152</v>
+        <v>224</v>
       </c>
       <c r="D20" t="n">
-        <v>91</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>159</v>
+        <v>61</v>
       </c>
       <c r="D21" t="n">
-        <v>85</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="C22" t="n">
-        <v>126</v>
+        <v>193</v>
       </c>
       <c r="D22" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="D23" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="C24" t="n">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="D24" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>59</v>
+        <v>203</v>
       </c>
       <c r="C25" t="n">
-        <v>84</v>
+        <v>234</v>
       </c>
       <c r="D25" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="C26" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -5860,7 +5972,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>352</t>
         </is>
       </c>
     </row>
@@ -5894,7 +6006,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>250</t>
         </is>
       </c>
     </row>
@@ -5928,7 +6040,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>154</t>
         </is>
       </c>
     </row>
@@ -5962,7 +6074,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>205</t>
         </is>
       </c>
     </row>
@@ -5996,7 +6108,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>254</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6142,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>142</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6176,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>81</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6210,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>188</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6278,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>146</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6312,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>76</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6482,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>315</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6550,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>74</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6584,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6754,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>110</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6822,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>264</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6924,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>73</t>
         </is>
       </c>
     </row>
@@ -6914,7 +7026,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -6948,7 +7060,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7332,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>203</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7468,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7570,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7604,7 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7706,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7914,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>352</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -7836,7 +7948,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>315</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -7854,136 +7966,136 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Vingegaard, Jonas</t>
+          <t>Girmay, Biniam</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/jonas-vingegaard-rasmussen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/biniam-girmay/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TVL</t>
+          <t>NSN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>264</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Girmay, Biniam</t>
+          <t>Philipsen, Jasper</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/biniam-girmay/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NSN</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Philipsen, Jasper</t>
+          <t>Vingegaard, Jonas</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jonas-vingegaard-rasmussen/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>TVL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>250</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>88.9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Del Toro, Isaac</t>
+          <t>Merlier, Tim</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/isaac-del-toro/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tim-merlier/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UAD</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8118,7 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -8024,34 +8136,34 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Merlier, Tim</t>
+          <t>Del Toro, Isaac</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tim-merlier/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/isaac-del-toro/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>UAD</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8186,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -8092,12 +8204,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Seixas, Paul</t>
+          <t>Kooij, Olav</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/paul-seixas/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/olav-kooij/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8108,30 +8220,30 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>44.4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Kooij, Olav</t>
+          <t>Seixas, Paul</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/olav-kooij/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/paul-seixas/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8142,41 +8254,41 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ayuso, Juan</t>
+          <t>Fretin, Milan</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/milan-fretin/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -8194,23 +8306,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Fretin, Milan</t>
+          <t>Ayuso, Juan</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/milan-fretin/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -8228,159 +8340,159 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Pidcock, Tom</t>
+          <t>Carapaz, Richard</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PQT</t>
+          <t>EFE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Carapaz, Richard</t>
+          <t>Pidcock, Tom</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>EFE</t>
+          <t>PQT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Simmons, Quinn</t>
+          <t>Poel, Mathieu van der</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/quinn-simmons/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mathieu-van-der-poel/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>76</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>44.4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Poel, Mathieu van der</t>
+          <t>Ackermann, Pascal</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mathieu-van-der-poel/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/pascal-ackermann/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>JAY</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ackermann, Pascal</t>
+          <t>Simmons, Quinn</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/pascal-ackermann/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/quinn-simmons/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JAY</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -8398,51 +8510,51 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Lipowitz, Florian</t>
+          <t>Vacek, Mathias</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/florian-lipowitz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mathias-vacek/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Vacek, Mathias</t>
+          <t>Lipowitz, Florian</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mathias-vacek/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/florian-lipowitz/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -8454,12 +8566,12 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
@@ -8482,7 +8594,7 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -8516,7 +8628,7 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -8636,46 +8748,46 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ganna, Filippo</t>
+          <t>Teunissen, Mike</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mike-teunissen/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>XAT</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Vauquelin, Kévin</t>
+          <t>Ganna, Filippo</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -8692,35 +8804,35 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Teunissen, Mike</t>
+          <t>Vauquelin, Kévin</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mike-teunissen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>XAT</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -8942,51 +9054,51 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Healy, Ben</t>
+          <t>Tiberi, Antonio</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/ben-healy/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/antonio-tiberi/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>EFE</t>
+          <t>TBV</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>O'Connor, Ben</t>
+          <t>Baarle, Dylan van</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/ben-o-connor/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/dylan-van-baarle/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>JAY</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -8998,29 +9110,29 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tiberi, Antonio</t>
+          <t>Healy, Ben</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/antonio-tiberi/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ben-healy/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TBV</t>
+          <t>EFE</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -9032,29 +9144,29 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Voisard, Yannis</t>
+          <t>O'Connor, Ben</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/yannis-voisard/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ben-o-connor/2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TUD</t>
+          <t>JAY</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -9066,35 +9178,35 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Aranburu, Álex</t>
+          <t>Voisard, Yannis</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/alex-aranburu/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/yannis-voisard/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>TUD</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
@@ -9112,17 +9224,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Denz, Nico</t>
+          <t>Aranburu, Álex</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/nico-denz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/alex-aranburu/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -9146,12 +9258,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Van Gils, Maxim</t>
+          <t>Denz, Nico</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/maxim-van-gils/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/nico-denz/2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -9168,69 +9280,69 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Uijtdebroeks, Cian</t>
+          <t>Van Gils, Maxim</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/maxim-van-gils/2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>44.4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Hirschi, Marc</t>
+          <t>Uijtdebroeks, Cian</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/marc-hirschi/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TUD</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -9248,51 +9360,51 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Arensman, Thymen</t>
+          <t>Hirschi, Marc</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/marc-hirschi/2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>TUD</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Baarle, Dylan van</t>
+          <t>Arensman, Thymen</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/dylan-van-baarle/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/thymen-arensman/2026</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -9304,12 +9416,12 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
@@ -9399,7 +9511,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">

--- a/data/dashboard.xlsx
+++ b/data/dashboard.xlsx
@@ -209,12 +209,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -277,12 +277,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -311,12 +311,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -345,12 +345,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$F$2:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -379,12 +379,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$G$2:$G$16</f>
             </numRef>
           </val>
         </ser>
@@ -413,12 +413,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$H$2:$H$16</f>
             </numRef>
           </val>
         </ser>
@@ -447,12 +447,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$I$2:$I$16</f>
             </numRef>
           </val>
         </ser>
@@ -481,12 +481,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$13</f>
+              <f>'STAR Verloop Algemeen (Pts)'!$J$2:$J$16</f>
             </numRef>
           </val>
         </ser>
@@ -602,12 +602,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$13</f>
+              <f>'Verloop GC-punten'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$B$2:$B$13</f>
+              <f>'Verloop GC-punten'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -636,12 +636,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$13</f>
+              <f>'Verloop GC-punten'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$C$2:$C$13</f>
+              <f>'Verloop GC-punten'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -670,12 +670,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$13</f>
+              <f>'Verloop GC-punten'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$D$2:$D$13</f>
+              <f>'Verloop GC-punten'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -704,12 +704,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$13</f>
+              <f>'Verloop GC-punten'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$E$2:$E$13</f>
+              <f>'Verloop GC-punten'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -738,12 +738,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$13</f>
+              <f>'Verloop GC-punten'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$F$2:$F$13</f>
+              <f>'Verloop GC-punten'!$F$2:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -772,12 +772,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$13</f>
+              <f>'Verloop GC-punten'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$G$2:$G$13</f>
+              <f>'Verloop GC-punten'!$G$2:$G$16</f>
             </numRef>
           </val>
         </ser>
@@ -806,12 +806,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$13</f>
+              <f>'Verloop GC-punten'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$H$2:$H$13</f>
+              <f>'Verloop GC-punten'!$H$2:$H$16</f>
             </numRef>
           </val>
         </ser>
@@ -840,12 +840,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$13</f>
+              <f>'Verloop GC-punten'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$I$2:$I$13</f>
+              <f>'Verloop GC-punten'!$I$2:$I$16</f>
             </numRef>
           </val>
         </ser>
@@ -874,12 +874,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop GC-punten'!$A$2:$A$13</f>
+              <f>'Verloop GC-punten'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop GC-punten'!$J$2:$J$13</f>
+              <f>'Verloop GC-punten'!$J$2:$J$16</f>
             </numRef>
           </val>
         </ser>
@@ -995,12 +995,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$B$2:$B$13</f>
+              <f>'Verloop Puntenklassement'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -1029,12 +1029,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$C$2:$C$13</f>
+              <f>'Verloop Puntenklassement'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -1063,12 +1063,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$D$2:$D$13</f>
+              <f>'Verloop Puntenklassement'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -1097,12 +1097,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$E$2:$E$13</f>
+              <f>'Verloop Puntenklassement'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -1131,12 +1131,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$F$2:$F$13</f>
+              <f>'Verloop Puntenklassement'!$F$2:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -1165,12 +1165,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$G$2:$G$13</f>
+              <f>'Verloop Puntenklassement'!$G$2:$G$16</f>
             </numRef>
           </val>
         </ser>
@@ -1199,12 +1199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$H$2:$H$13</f>
+              <f>'Verloop Puntenklassement'!$H$2:$H$16</f>
             </numRef>
           </val>
         </ser>
@@ -1233,12 +1233,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$I$2:$I$13</f>
+              <f>'Verloop Puntenklassement'!$I$2:$I$16</f>
             </numRef>
           </val>
         </ser>
@@ -1267,12 +1267,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Puntenklassement'!$A$2:$A$13</f>
+              <f>'Verloop Puntenklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Puntenklassement'!$J$2:$J$13</f>
+              <f>'Verloop Puntenklassement'!$J$2:$J$16</f>
             </numRef>
           </val>
         </ser>
@@ -1388,12 +1388,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$B$2:$B$13</f>
+              <f>'Verloop Bergklassement'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -1422,12 +1422,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$C$2:$C$13</f>
+              <f>'Verloop Bergklassement'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -1456,12 +1456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$D$2:$D$13</f>
+              <f>'Verloop Bergklassement'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -1490,12 +1490,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$E$2:$E$13</f>
+              <f>'Verloop Bergklassement'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -1524,12 +1524,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$F$2:$F$13</f>
+              <f>'Verloop Bergklassement'!$F$2:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -1558,12 +1558,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$G$2:$G$13</f>
+              <f>'Verloop Bergklassement'!$G$2:$G$16</f>
             </numRef>
           </val>
         </ser>
@@ -1592,12 +1592,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$H$2:$H$13</f>
+              <f>'Verloop Bergklassement'!$H$2:$H$16</f>
             </numRef>
           </val>
         </ser>
@@ -1626,12 +1626,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$I$2:$I$13</f>
+              <f>'Verloop Bergklassement'!$I$2:$I$16</f>
             </numRef>
           </val>
         </ser>
@@ -1660,12 +1660,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Verloop Bergklassement'!$A$2:$A$13</f>
+              <f>'Verloop Bergklassement'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Verloop Bergklassement'!$J$2:$J$13</f>
+              <f>'Verloop Bergklassement'!$J$2:$J$16</f>
             </numRef>
           </val>
         </ser>
@@ -2217,37 +2217,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>487</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>674</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -2255,42 +2255,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>426</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>554</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2298,42 +2298,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>353</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>425</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2341,42 +2341,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>353</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>592</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2389,37 +2389,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>474</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>496</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -2432,27 +2432,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>449</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>611</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -2475,27 +2475,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>461</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>493</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2518,27 +2518,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>351</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>514</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2561,27 +2561,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>822</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>404</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>608</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2663,22 +2663,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>276</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>162</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>468</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2696,32 +2696,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>496</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>311</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>384</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2739,32 +2739,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>528</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>281</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>267</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>384</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,32 +2782,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>476</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>255</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>446</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>87</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2835,22 +2835,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>296</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>214</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>360</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,32 +2868,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>363</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>263</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2911,32 +2911,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>302</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>227</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>308</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,32 +2954,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>272</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>198</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>204</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>372</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3007,22 +3007,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>287</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>358</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>822</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,32 +3094,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>196</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>487</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3137,42 +3137,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>474</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3185,22 +3185,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>184</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>461</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3223,27 +3223,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>181</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>158</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>449</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3266,27 +3266,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>151</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>186</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>426</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>131</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>404</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -3352,7 +3352,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3362,22 +3362,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>166</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>353</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -3395,42 +3395,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>145</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>353</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -3438,32 +3438,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>152</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>351</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -3525,12 +3525,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -3553,12 +3553,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>98</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -3716,12 +3716,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -3744,12 +3744,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4255,6 +4255,108 @@
         <v>61</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stage 13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>139</v>
+      </c>
+      <c r="C14" t="n">
+        <v>118</v>
+      </c>
+      <c r="D14" t="n">
+        <v>99</v>
+      </c>
+      <c r="E14" t="n">
+        <v>110</v>
+      </c>
+      <c r="F14" t="n">
+        <v>68</v>
+      </c>
+      <c r="G14" t="n">
+        <v>133</v>
+      </c>
+      <c r="H14" t="n">
+        <v>104</v>
+      </c>
+      <c r="I14" t="n">
+        <v>157</v>
+      </c>
+      <c r="J14" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stage 14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>189</v>
+      </c>
+      <c r="C15" t="n">
+        <v>223</v>
+      </c>
+      <c r="D15" t="n">
+        <v>219</v>
+      </c>
+      <c r="E15" t="n">
+        <v>256</v>
+      </c>
+      <c r="F15" t="n">
+        <v>245</v>
+      </c>
+      <c r="G15" t="n">
+        <v>231</v>
+      </c>
+      <c r="H15" t="n">
+        <v>295</v>
+      </c>
+      <c r="I15" t="n">
+        <v>216</v>
+      </c>
+      <c r="J15" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stage 15</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>199</v>
+      </c>
+      <c r="C16" t="n">
+        <v>195</v>
+      </c>
+      <c r="D16" t="n">
+        <v>163</v>
+      </c>
+      <c r="E16" t="n">
+        <v>216</v>
+      </c>
+      <c r="F16" t="n">
+        <v>232</v>
+      </c>
+      <c r="G16" t="n">
+        <v>212</v>
+      </c>
+      <c r="H16" t="n">
+        <v>288</v>
+      </c>
+      <c r="I16" t="n">
+        <v>264</v>
+      </c>
+      <c r="J16" t="n">
+        <v>259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4267,7 +4369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4742,6 +4844,108 @@
         <v>46</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stage 13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>36</v>
+      </c>
+      <c r="C14" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" t="n">
+        <v>43</v>
+      </c>
+      <c r="E14" t="n">
+        <v>45</v>
+      </c>
+      <c r="F14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G14" t="n">
+        <v>44</v>
+      </c>
+      <c r="H14" t="n">
+        <v>50</v>
+      </c>
+      <c r="I14" t="n">
+        <v>47</v>
+      </c>
+      <c r="J14" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stage 14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>30</v>
+      </c>
+      <c r="C15" t="n">
+        <v>44</v>
+      </c>
+      <c r="D15" t="n">
+        <v>41</v>
+      </c>
+      <c r="E15" t="n">
+        <v>49</v>
+      </c>
+      <c r="F15" t="n">
+        <v>41</v>
+      </c>
+      <c r="G15" t="n">
+        <v>42</v>
+      </c>
+      <c r="H15" t="n">
+        <v>53</v>
+      </c>
+      <c r="I15" t="n">
+        <v>45</v>
+      </c>
+      <c r="J15" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stage 15</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>37</v>
+      </c>
+      <c r="C16" t="n">
+        <v>41</v>
+      </c>
+      <c r="D16" t="n">
+        <v>34</v>
+      </c>
+      <c r="E16" t="n">
+        <v>42</v>
+      </c>
+      <c r="F16" t="n">
+        <v>34</v>
+      </c>
+      <c r="G16" t="n">
+        <v>31</v>
+      </c>
+      <c r="H16" t="n">
+        <v>51</v>
+      </c>
+      <c r="I16" t="n">
+        <v>46</v>
+      </c>
+      <c r="J16" t="n">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4754,7 +4958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5196,6 +5400,108 @@
         <v>11</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stage 13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>69</v>
+      </c>
+      <c r="C14" t="n">
+        <v>58</v>
+      </c>
+      <c r="D14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" t="n">
+        <v>45</v>
+      </c>
+      <c r="F14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
+      </c>
+      <c r="H14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I14" t="n">
+        <v>66</v>
+      </c>
+      <c r="J14" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stage 14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>79</v>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="n">
+        <v>88</v>
+      </c>
+      <c r="E15" t="n">
+        <v>104</v>
+      </c>
+      <c r="F15" t="n">
+        <v>82</v>
+      </c>
+      <c r="G15" t="n">
+        <v>90</v>
+      </c>
+      <c r="H15" t="n">
+        <v>131</v>
+      </c>
+      <c r="I15" t="n">
+        <v>102</v>
+      </c>
+      <c r="J15" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stage 15</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>76</v>
+      </c>
+      <c r="C16" t="n">
+        <v>80</v>
+      </c>
+      <c r="D16" t="n">
+        <v>68</v>
+      </c>
+      <c r="E16" t="n">
+        <v>86</v>
+      </c>
+      <c r="F16" t="n">
+        <v>85</v>
+      </c>
+      <c r="G16" t="n">
+        <v>76</v>
+      </c>
+      <c r="H16" t="n">
+        <v>115</v>
+      </c>
+      <c r="I16" t="n">
+        <v>91</v>
+      </c>
+      <c r="J16" t="n">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5208,7 +5514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5492,6 +5798,102 @@
       </c>
       <c r="G13" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stage 13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>24</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
+        <v>24</v>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stage 14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>66</v>
+      </c>
+      <c r="C15" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" t="n">
+        <v>81</v>
+      </c>
+      <c r="E15" t="n">
+        <v>89</v>
+      </c>
+      <c r="F15" t="n">
+        <v>108</v>
+      </c>
+      <c r="G15" t="n">
+        <v>85</v>
+      </c>
+      <c r="H15" t="n">
+        <v>97</v>
+      </c>
+      <c r="I15" t="n">
+        <v>55</v>
+      </c>
+      <c r="J15" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stage 15</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>72</v>
+      </c>
+      <c r="C16" t="n">
+        <v>60</v>
+      </c>
+      <c r="D16" t="n">
+        <v>59</v>
+      </c>
+      <c r="E16" t="n">
+        <v>74</v>
+      </c>
+      <c r="F16" t="n">
+        <v>99</v>
+      </c>
+      <c r="G16" t="n">
+        <v>91</v>
+      </c>
+      <c r="H16" t="n">
+        <v>108</v>
+      </c>
+      <c r="I16" t="n">
+        <v>113</v>
+      </c>
+      <c r="J16" t="n">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -5554,33 +5956,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>152</v>
+        <v>216</v>
       </c>
       <c r="C5" t="n">
-        <v>224</v>
+        <v>264</v>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>99</v>
+        <v>225</v>
       </c>
       <c r="C6" t="n">
-        <v>154</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -5590,109 +5992,109 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C7" t="n">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="D7" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>154</v>
+        <v>295</v>
       </c>
       <c r="C8" t="n">
-        <v>193</v>
+        <v>288</v>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>159</v>
+        <v>245</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160</v>
+        <v>231</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>126</v>
+        <v>223</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>84</v>
+        <v>256</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>216</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64</v>
+        <v>219</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>163</v>
       </c>
       <c r="D13" t="n">
-        <v>-3</v>
+        <v>-56</v>
       </c>
     </row>
     <row r="16">
@@ -5727,145 +6129,145 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Not_Kermit</t>
+          <t>Yellow bitch</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="C18" t="n">
-        <v>154</v>
+        <v>259</v>
       </c>
       <c r="D18" t="n">
-        <v>67</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SexySeixas</t>
+          <t>Tour MondAIl</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="C19" t="n">
-        <v>191</v>
+        <v>264</v>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ko-fidis</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C20" t="n">
-        <v>224</v>
+        <v>288</v>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Yellow bitch</t>
+          <t>Not_Kermit</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="C21" t="n">
-        <v>61</v>
+        <v>232</v>
       </c>
       <c r="D21" t="n">
-        <v>41</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>Immer geradeaus</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="C22" t="n">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="D22" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Immer geradeaus</t>
+          <t>Pan y aqua</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>101</v>
+        <v>174</v>
       </c>
       <c r="C23" t="n">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="D23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Belahu</t>
+          <t>Ko-fidis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="C24" t="n">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="D24" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alegría</t>
+          <t>Belahu</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="C25" t="n">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tour MondAIl</t>
+          <t>Alegría</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="C26" t="n">
-        <v>89</v>
+        <v>199</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>-33</v>
       </c>
     </row>
   </sheetData>
@@ -5972,7 +6374,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>479</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6408,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>300</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6442,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>241</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6476,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>209</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6510,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>311</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6544,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>221</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6578,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>146</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6612,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>267</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6646,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6680,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6748,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6850,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>95</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6884,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>372</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6918,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>164</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6986,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>142</t>
         </is>
       </c>
     </row>
@@ -6686,7 +7088,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -6788,7 +7190,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -6822,7 +7224,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>310</t>
         </is>
       </c>
     </row>
@@ -6856,7 +7258,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -6890,7 +7292,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -6924,7 +7326,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>122</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7598,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7632,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7700,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7734,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>233</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7836,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7870,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>124</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7972,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -7604,7 +8006,7 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -7706,7 +8108,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>73</t>
         </is>
       </c>
     </row>
@@ -7740,7 +8142,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -7774,7 +8176,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -7842,7 +8244,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -7914,7 +8316,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>479</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -7948,7 +8350,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>372</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -7966,68 +8368,68 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Girmay, Biniam</t>
+          <t>Philipsen, Jasper</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/biniam-girmay/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NSN</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>311</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Philipsen, Jasper</t>
+          <t>Girmay, Biniam</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/jasper-philipsen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/biniam-girmay/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>NSN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>310</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8452,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -8068,125 +8470,125 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Merlier, Tim</t>
+          <t>Del Toro, Isaac</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tim-merlier/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/isaac-del-toro/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>UAD</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>267</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kanter, Max</t>
+          <t>Evenepoel, Remco</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/max-kanter/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/remco-evenepoel/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>XAT</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>241</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Del Toro, Isaac</t>
+          <t>Kanter, Max</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/isaac-del-toro/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/max-kanter/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>UAD</t>
+          <t>XAT</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>233</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Evenepoel, Remco</t>
+          <t>Seixas, Paul</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/remco-evenepoel/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/paul-seixas/2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>221</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -8204,261 +8606,261 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kooij, Olav</t>
+          <t>Merlier, Tim</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/olav-kooij/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tim-merlier/2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DCT</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>209</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>66.7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Seixas, Paul</t>
+          <t>Pidcock, Tom</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/paul-seixas/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DCT</t>
+          <t>PQT</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Fretin, Milan</t>
+          <t>Kooij, Olav</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/milan-fretin/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/olav-kooij/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>44.4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ayuso, Juan</t>
+          <t>Carapaz, Richard</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>EFE</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Carapaz, Richard</t>
+          <t>Ayuso, Juan</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/richard-carapaz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/juan-ayuso/2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>EFE</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Pidcock, Tom</t>
+          <t>Paret-Peintre, Valentin</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tom-pidcock/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/valentin-paret-peintre/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PQT</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Poel, Mathieu van der</t>
+          <t>Simmons, Quinn</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mathieu-van-der-poel/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/quinn-simmons/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>APT</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ackermann, Pascal</t>
+          <t>Fretin, Milan</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/pascal-ackermann/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/milan-fretin/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JAY</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -8476,125 +8878,125 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Simmons, Quinn</t>
+          <t>Lipowitz, Florian</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/quinn-simmons/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/florian-lipowitz/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Vacek, Mathias</t>
+          <t>Poel, Mathieu van der</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mathias-vacek/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mathieu-van-der-poel/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LTK</t>
+          <t>APT</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>76</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>44.4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Lipowitz, Florian</t>
+          <t>Ackermann, Pascal</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/florian-lipowitz/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/pascal-ackermann/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>JAY</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Paret-Peintre, Valentin</t>
+          <t>Vacek, Mathias</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/valentin-paret-peintre/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mathias-vacek/2026</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>LTK</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -8646,272 +9048,272 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bauhaus, Phil</t>
+          <t>Vauquelin, Kévin</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/phil-bauhaus/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TBV</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Castrillo, Pablo</t>
+          <t>Bauhaus, Phil</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/pablo-castrillo/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/phil-bauhaus/2026</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>TBV</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Van Eetvelt, Lennert</t>
+          <t>Teunissen, Mike</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/lennert-van-eetvelt/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/mike-teunissen/2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LOI</t>
+          <t>XAT</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Teunissen, Mike</t>
+          <t>Van Gils, Maxim</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/mike-teunissen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/maxim-van-gils/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>XAT</t>
+          <t>RBH</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>44.4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ganna, Filippo</t>
+          <t>Castrillo, Pablo</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/pablo-castrillo/2026</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Vauquelin, Kévin</t>
+          <t>Van Eetvelt, Lennert</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/kevin-vauquelin/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/lennert-van-eetvelt/2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>IGD</t>
+          <t>LOI</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Van Wilder, Ilan</t>
+          <t>Wellens, Tim</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/tim-wellens/2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>UAD</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>55.6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Wellens, Tim</t>
+          <t>Ganna, Filippo</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/tim-wellens/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/filippo-ganna/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>UAD</t>
+          <t>IGD</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>22.2</t>
         </is>
       </c>
     </row>
@@ -8934,7 +9336,7 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -8952,57 +9354,57 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Alaphilippe, Julian</t>
+          <t>Van Wilder, Ilan</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/julian-alaphilippe/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ilan-van-wilder/2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TUD</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cort, Magnus</t>
+          <t>Voisard, Yannis</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/magnus-cort-nielsen/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/yannis-voisard/2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>UXM</t>
+          <t>TUD</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -9020,23 +9422,23 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Campenaerts, Victor</t>
+          <t>Healy, Ben</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/victor-campenaerts/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/ben-healy/2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TVL</t>
+          <t>EFE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -9054,57 +9456,57 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tiberi, Antonio</t>
+          <t>Alaphilippe, Julian</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/antonio-tiberi/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/julian-alaphilippe/2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TBV</t>
+          <t>TUD</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Baarle, Dylan van</t>
+          <t>Cort, Magnus</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/dylan-van-baarle/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/magnus-cort-nielsen/2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SOQ</t>
+          <t>UXM</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -9122,23 +9524,23 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Healy, Ben</t>
+          <t>Campenaerts, Victor</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/ben-healy/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/victor-campenaerts/2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>EFE</t>
+          <t>TVL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -9172,7 +9574,7 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -9190,23 +9592,23 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Voisard, Yannis</t>
+          <t>Tiberi, Antonio</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/yannis-voisard/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/antonio-tiberi/2026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TUD</t>
+          <t>TBV</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
@@ -9224,23 +9626,23 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Aranburu, Álex</t>
+          <t>Baarle, Dylan van</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/alex-aranburu/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/dylan-van-baarle/2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>SOQ</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -9274,7 +9676,7 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -9292,57 +9694,57 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Van Gils, Maxim</t>
+          <t>Hirschi, Marc</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/maxim-van-gils/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/marc-hirschi/2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>RBH</t>
+          <t>TUD</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Uijtdebroeks, Cian</t>
+          <t>Aranburu, Álex</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/alex-aranburu/2026</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MOV</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -9360,23 +9762,23 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Hirschi, Marc</t>
+          <t>Uijtdebroeks, Cian</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.worldcyclingstats.com/en/rider/marc-hirschi/2026</t>
+          <t>https://www.worldcyclingstats.com/en/rider/cian-uijtdebroeks/2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TUD</t>
+          <t>MOV</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -9511,7 +9913,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Pan y aqua</t>
+          <t>SexySeixas</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
